--- a/public/templates/RFS_TEMPLATE.xlsx
+++ b/public/templates/RFS_TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/59650d1564ea21d1/Desktop/System Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{5D7ECA62-A79A-4C4F-9665-9516C8D8661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A1BDC39-4A9D-4D0E-BFB4-BEAFD5619E9A}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{5D7ECA62-A79A-4C4F-9665-9516C8D8661E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{445A31D8-4DE9-40DD-BD5E-131A564A61BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="66">
   <si>
     <t>Document No.</t>
   </si>
@@ -262,6 +262,9 @@
   <si>
     <t>{{APPROVED_BY}}</t>
   </si>
+  <si>
+    <t>Southcoast Metal Enterprise, Inc.</t>
+  </si>
 </sst>
 </file>
 
@@ -273,7 +276,7 @@
     <numFmt numFmtId="166" formatCode="&quot;₱&quot;#,##0.00"/>
     <numFmt numFmtId="167" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -422,6 +425,17 @@
       <name val="Arial Nova"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1242,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1257,8 +1271,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1276,8 +1288,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1314,7 +1324,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1400,6 +1409,33 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1752,15 +1788,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1906,16 +1933,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>83345</xdr:rowOff>
+      <xdr:col>73</xdr:col>
+      <xdr:colOff>26504</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>36963</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>53578</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>53578</xdr:rowOff>
+      <xdr:col>115</xdr:col>
+      <xdr:colOff>46952</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146343</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1932,8 +1959,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="235585"/>
-          <a:ext cx="4749165" cy="427355"/>
+          <a:off x="7898295" y="1819380"/>
+          <a:ext cx="4751474" cy="427433"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1954,13 +1981,6 @@
               <a:spcPts val="1500"/>
             </a:lnSpc>
           </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1800" b="1">
-              <a:effectLst/>
-              <a:latin typeface="Tahoma" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Southcoast Metal Enterprise, Inc.</a:t>
-          </a:r>
           <a:endParaRPr lang="en-PH" sz="1800">
             <a:effectLst/>
           </a:endParaRPr>
@@ -3991,584 +4011,594 @@
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="201"/>
-      <c r="O1" s="201"/>
-      <c r="P1" s="201"/>
-      <c r="Q1" s="201"/>
-      <c r="R1" s="201"/>
-      <c r="S1" s="201"/>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="201"/>
-      <c r="W1" s="201"/>
-      <c r="X1" s="201"/>
-      <c r="Y1" s="201"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="201"/>
-      <c r="AB1" s="201"/>
-      <c r="AC1" s="201"/>
-      <c r="AD1" s="201"/>
-      <c r="AE1" s="201"/>
-      <c r="AF1" s="201"/>
-      <c r="AG1" s="201"/>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="201"/>
-      <c r="AJ1" s="201"/>
-      <c r="AK1" s="201"/>
-      <c r="AL1" s="201"/>
-      <c r="AM1" s="201"/>
-      <c r="AN1" s="201"/>
-      <c r="AO1" s="201"/>
-      <c r="AP1" s="201"/>
-      <c r="AQ1" s="201"/>
-      <c r="AR1" s="201"/>
-      <c r="AS1" s="96" t="s">
+      <c r="I1" s="76" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="77"/>
+      <c r="T1" s="77"/>
+      <c r="U1" s="77"/>
+      <c r="V1" s="77"/>
+      <c r="W1" s="77"/>
+      <c r="X1" s="77"/>
+      <c r="Y1" s="77"/>
+      <c r="Z1" s="77"/>
+      <c r="AA1" s="77"/>
+      <c r="AB1" s="77"/>
+      <c r="AC1" s="77"/>
+      <c r="AD1" s="77"/>
+      <c r="AE1" s="77"/>
+      <c r="AF1" s="77"/>
+      <c r="AG1" s="77"/>
+      <c r="AH1" s="77"/>
+      <c r="AI1" s="77"/>
+      <c r="AJ1" s="77"/>
+      <c r="AK1" s="77"/>
+      <c r="AL1" s="77"/>
+      <c r="AM1" s="77"/>
+      <c r="AN1" s="77"/>
+      <c r="AO1" s="77"/>
+      <c r="AP1" s="77"/>
+      <c r="AQ1" s="77"/>
+      <c r="AR1" s="78"/>
+      <c r="AS1" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="AT1" s="97"/>
-      <c r="AU1" s="97"/>
-      <c r="AV1" s="97"/>
-      <c r="AW1" s="97"/>
-      <c r="AX1" s="97"/>
-      <c r="AY1" s="97"/>
-      <c r="AZ1" s="97"/>
-      <c r="BA1" s="10" t="s">
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="101"/>
+      <c r="AX1" s="101"/>
+      <c r="AY1" s="101"/>
+      <c r="AZ1" s="101"/>
+      <c r="BA1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="BB1" s="98" t="s">
+      <c r="BB1" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="98"/>
-      <c r="BD1" s="98"/>
-      <c r="BE1" s="98"/>
-      <c r="BF1" s="98"/>
-      <c r="BG1" s="98"/>
-      <c r="BH1" s="98"/>
-      <c r="BI1" s="98"/>
-      <c r="BJ1" s="98"/>
-      <c r="BK1" s="99"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="102"/>
+      <c r="BK1" s="103"/>
     </row>
     <row r="2" spans="1:70" ht="12" customHeight="1">
-      <c r="A2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="N2" s="202"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="202"/>
-      <c r="Q2" s="202"/>
-      <c r="R2" s="202"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="202"/>
-      <c r="U2" s="202"/>
-      <c r="V2" s="202"/>
-      <c r="W2" s="202"/>
-      <c r="X2" s="202"/>
-      <c r="Y2" s="202"/>
-      <c r="Z2" s="202"/>
-      <c r="AA2" s="202"/>
-      <c r="AB2" s="202"/>
-      <c r="AC2" s="202"/>
-      <c r="AD2" s="202"/>
-      <c r="AE2" s="202"/>
-      <c r="AF2" s="202"/>
-      <c r="AG2" s="202"/>
-      <c r="AH2" s="202"/>
-      <c r="AI2" s="202"/>
-      <c r="AJ2" s="202"/>
-      <c r="AK2" s="202"/>
-      <c r="AL2" s="202"/>
-      <c r="AM2" s="202"/>
-      <c r="AN2" s="202"/>
-      <c r="AO2" s="202"/>
-      <c r="AP2" s="202"/>
-      <c r="AQ2" s="202"/>
-      <c r="AR2" s="202"/>
-      <c r="AS2" s="100" t="s">
+      <c r="A2" s="9"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="80"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="80"/>
+      <c r="AO2" s="80"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="81"/>
+      <c r="AS2" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="AT2" s="101"/>
-      <c r="AU2" s="101"/>
-      <c r="AV2" s="101"/>
-      <c r="AW2" s="101"/>
-      <c r="AX2" s="101"/>
-      <c r="AY2" s="101"/>
-      <c r="AZ2" s="101"/>
-      <c r="BA2" s="13" t="s">
+      <c r="AT2" s="105"/>
+      <c r="AU2" s="105"/>
+      <c r="AV2" s="105"/>
+      <c r="AW2" s="105"/>
+      <c r="AX2" s="105"/>
+      <c r="AY2" s="105"/>
+      <c r="AZ2" s="105"/>
+      <c r="BA2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="BB2" s="102"/>
-      <c r="BC2" s="102"/>
-      <c r="BD2" s="102"/>
-      <c r="BE2" s="102"/>
-      <c r="BF2" s="102"/>
-      <c r="BG2" s="102"/>
-      <c r="BH2" s="102"/>
-      <c r="BI2" s="102"/>
-      <c r="BJ2" s="102"/>
-      <c r="BK2" s="103"/>
+      <c r="BB2" s="106"/>
+      <c r="BC2" s="106"/>
+      <c r="BD2" s="106"/>
+      <c r="BE2" s="106"/>
+      <c r="BF2" s="106"/>
+      <c r="BG2" s="106"/>
+      <c r="BH2" s="106"/>
+      <c r="BI2" s="106"/>
+      <c r="BJ2" s="106"/>
+      <c r="BK2" s="107"/>
     </row>
     <row r="3" spans="1:70" ht="12" customHeight="1">
-      <c r="A3" s="11"/>
-      <c r="I3" s="12"/>
-      <c r="N3" s="202"/>
-      <c r="O3" s="202"/>
-      <c r="P3" s="202"/>
-      <c r="Q3" s="202"/>
-      <c r="R3" s="202"/>
-      <c r="S3" s="202"/>
-      <c r="T3" s="202"/>
-      <c r="U3" s="202"/>
-      <c r="V3" s="202"/>
-      <c r="W3" s="202"/>
-      <c r="X3" s="202"/>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
-      <c r="AA3" s="202"/>
-      <c r="AB3" s="202"/>
-      <c r="AC3" s="202"/>
-      <c r="AD3" s="202"/>
-      <c r="AE3" s="202"/>
-      <c r="AF3" s="202"/>
-      <c r="AG3" s="202"/>
-      <c r="AH3" s="202"/>
-      <c r="AI3" s="202"/>
-      <c r="AJ3" s="202"/>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="202"/>
-      <c r="AN3" s="202"/>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
-      <c r="AQ3" s="202"/>
-      <c r="AR3" s="202"/>
-      <c r="AS3" s="100" t="s">
+      <c r="A3" s="9"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="80"/>
+      <c r="L3" s="80"/>
+      <c r="M3" s="80"/>
+      <c r="N3" s="80"/>
+      <c r="O3" s="80"/>
+      <c r="P3" s="80"/>
+      <c r="Q3" s="80"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="80"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="80"/>
+      <c r="AC3" s="80"/>
+      <c r="AD3" s="80"/>
+      <c r="AE3" s="80"/>
+      <c r="AF3" s="80"/>
+      <c r="AG3" s="80"/>
+      <c r="AH3" s="80"/>
+      <c r="AI3" s="80"/>
+      <c r="AJ3" s="80"/>
+      <c r="AK3" s="80"/>
+      <c r="AL3" s="80"/>
+      <c r="AM3" s="80"/>
+      <c r="AN3" s="80"/>
+      <c r="AO3" s="80"/>
+      <c r="AP3" s="80"/>
+      <c r="AQ3" s="80"/>
+      <c r="AR3" s="81"/>
+      <c r="AS3" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="AT3" s="101"/>
-      <c r="AU3" s="101"/>
-      <c r="AV3" s="101"/>
-      <c r="AW3" s="101"/>
-      <c r="AX3" s="101"/>
-      <c r="AY3" s="101"/>
-      <c r="AZ3" s="101"/>
-      <c r="BA3" s="13" t="s">
+      <c r="AT3" s="105"/>
+      <c r="AU3" s="105"/>
+      <c r="AV3" s="105"/>
+      <c r="AW3" s="105"/>
+      <c r="AX3" s="105"/>
+      <c r="AY3" s="105"/>
+      <c r="AZ3" s="105"/>
+      <c r="BA3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="BB3" s="102"/>
-      <c r="BC3" s="102"/>
-      <c r="BD3" s="102"/>
-      <c r="BE3" s="102"/>
-      <c r="BF3" s="102"/>
-      <c r="BG3" s="102"/>
-      <c r="BH3" s="102"/>
-      <c r="BI3" s="102"/>
-      <c r="BJ3" s="102"/>
-      <c r="BK3" s="103"/>
+      <c r="BB3" s="106"/>
+      <c r="BC3" s="106"/>
+      <c r="BD3" s="106"/>
+      <c r="BE3" s="106"/>
+      <c r="BF3" s="106"/>
+      <c r="BG3" s="106"/>
+      <c r="BH3" s="106"/>
+      <c r="BI3" s="106"/>
+      <c r="BJ3" s="106"/>
+      <c r="BK3" s="107"/>
     </row>
     <row r="4" spans="1:70" ht="12" customHeight="1" thickBot="1">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="203"/>
-      <c r="O4" s="203"/>
-      <c r="P4" s="203"/>
-      <c r="Q4" s="203"/>
-      <c r="R4" s="203"/>
-      <c r="S4" s="203"/>
-      <c r="T4" s="203"/>
-      <c r="U4" s="203"/>
-      <c r="V4" s="203"/>
-      <c r="W4" s="203"/>
-      <c r="X4" s="203"/>
-      <c r="Y4" s="203"/>
-      <c r="Z4" s="203"/>
-      <c r="AA4" s="203"/>
-      <c r="AB4" s="203"/>
-      <c r="AC4" s="203"/>
-      <c r="AD4" s="203"/>
-      <c r="AE4" s="203"/>
-      <c r="AF4" s="203"/>
-      <c r="AG4" s="203"/>
-      <c r="AH4" s="203"/>
-      <c r="AI4" s="203"/>
-      <c r="AJ4" s="203"/>
-      <c r="AK4" s="203"/>
-      <c r="AL4" s="203"/>
-      <c r="AM4" s="203"/>
-      <c r="AN4" s="203"/>
-      <c r="AO4" s="203"/>
-      <c r="AP4" s="203"/>
-      <c r="AQ4" s="203"/>
-      <c r="AR4" s="203"/>
-      <c r="AS4" s="104" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Y4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AD4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AI4" s="83"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="83"/>
+      <c r="AL4" s="83"/>
+      <c r="AM4" s="83"/>
+      <c r="AN4" s="83"/>
+      <c r="AO4" s="83"/>
+      <c r="AP4" s="83"/>
+      <c r="AQ4" s="83"/>
+      <c r="AR4" s="84"/>
+      <c r="AS4" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="AT4" s="105"/>
-      <c r="AU4" s="105"/>
-      <c r="AV4" s="105"/>
-      <c r="AW4" s="105"/>
-      <c r="AX4" s="105"/>
-      <c r="AY4" s="105"/>
-      <c r="AZ4" s="105"/>
-      <c r="BA4" s="19" t="s">
+      <c r="AT4" s="109"/>
+      <c r="AU4" s="109"/>
+      <c r="AV4" s="109"/>
+      <c r="AW4" s="109"/>
+      <c r="AX4" s="109"/>
+      <c r="AY4" s="109"/>
+      <c r="AZ4" s="109"/>
+      <c r="BA4" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="BB4" s="106"/>
-      <c r="BC4" s="106"/>
-      <c r="BD4" s="106"/>
-      <c r="BE4" s="106"/>
-      <c r="BF4" s="106"/>
-      <c r="BG4" s="106"/>
-      <c r="BH4" s="106"/>
-      <c r="BI4" s="106"/>
-      <c r="BJ4" s="106"/>
-      <c r="BK4" s="107"/>
+      <c r="BB4" s="110"/>
+      <c r="BC4" s="110"/>
+      <c r="BD4" s="110"/>
+      <c r="BE4" s="110"/>
+      <c r="BF4" s="110"/>
+      <c r="BG4" s="110"/>
+      <c r="BH4" s="110"/>
+      <c r="BI4" s="110"/>
+      <c r="BJ4" s="110"/>
+      <c r="BK4" s="111"/>
     </row>
     <row r="5" spans="1:70" ht="12" customHeight="1">
-      <c r="A5" s="11"/>
-      <c r="I5" s="204" t="s">
+      <c r="A5" s="9"/>
+      <c r="I5" s="205" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="194"/>
-      <c r="K5" s="194"/>
-      <c r="L5" s="194"/>
-      <c r="M5" s="194"/>
-      <c r="N5" s="172" t="s">
+      <c r="J5" s="198"/>
+      <c r="K5" s="198"/>
+      <c r="L5" s="198"/>
+      <c r="M5" s="198"/>
+      <c r="N5" s="176" t="s">
         <v>1</v>
       </c>
-      <c r="O5" s="207" t="s">
+      <c r="O5" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="207"/>
-      <c r="Q5" s="207"/>
-      <c r="R5" s="207"/>
-      <c r="S5" s="207"/>
-      <c r="T5" s="207"/>
-      <c r="U5" s="207"/>
-      <c r="V5" s="207"/>
-      <c r="W5" s="207"/>
-      <c r="X5" s="207"/>
-      <c r="Y5" s="207"/>
-      <c r="Z5" s="207"/>
-      <c r="AA5" s="207"/>
-      <c r="AB5" s="207"/>
-      <c r="AC5" s="207"/>
-      <c r="AD5" s="207"/>
-      <c r="AE5" s="207"/>
-      <c r="AF5" s="207"/>
-      <c r="AG5" s="207"/>
-      <c r="AH5" s="207"/>
-      <c r="AI5" s="207"/>
-      <c r="AJ5" s="207"/>
-      <c r="AK5" s="207"/>
-      <c r="AL5" s="207"/>
-      <c r="AM5" s="207"/>
-      <c r="AN5" s="207"/>
-      <c r="AO5" s="207"/>
-      <c r="AP5" s="207"/>
-      <c r="AQ5" s="207"/>
-      <c r="AR5" s="208"/>
-      <c r="AS5" s="108" t="s">
+      <c r="P5" s="208"/>
+      <c r="Q5" s="208"/>
+      <c r="R5" s="208"/>
+      <c r="S5" s="208"/>
+      <c r="T5" s="208"/>
+      <c r="U5" s="208"/>
+      <c r="V5" s="208"/>
+      <c r="W5" s="208"/>
+      <c r="X5" s="208"/>
+      <c r="Y5" s="208"/>
+      <c r="Z5" s="208"/>
+      <c r="AA5" s="208"/>
+      <c r="AB5" s="208"/>
+      <c r="AC5" s="208"/>
+      <c r="AD5" s="208"/>
+      <c r="AE5" s="208"/>
+      <c r="AF5" s="208"/>
+      <c r="AG5" s="208"/>
+      <c r="AH5" s="208"/>
+      <c r="AI5" s="208"/>
+      <c r="AJ5" s="208"/>
+      <c r="AK5" s="208"/>
+      <c r="AL5" s="208"/>
+      <c r="AM5" s="208"/>
+      <c r="AN5" s="208"/>
+      <c r="AO5" s="208"/>
+      <c r="AP5" s="208"/>
+      <c r="AQ5" s="208"/>
+      <c r="AR5" s="209"/>
+      <c r="AS5" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="AT5" s="109"/>
-      <c r="AU5" s="109"/>
-      <c r="AV5" s="109"/>
-      <c r="AW5" s="109"/>
-      <c r="AX5" s="109"/>
-      <c r="AY5" s="109"/>
-      <c r="AZ5" s="109"/>
-      <c r="BA5" s="20"/>
-      <c r="BB5" s="110" t="s">
+      <c r="AT5" s="113"/>
+      <c r="AU5" s="113"/>
+      <c r="AV5" s="113"/>
+      <c r="AW5" s="113"/>
+      <c r="AX5" s="113"/>
+      <c r="AY5" s="113"/>
+      <c r="AZ5" s="113"/>
+      <c r="BA5" s="16"/>
+      <c r="BB5" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="BC5" s="110"/>
-      <c r="BD5" s="110"/>
-      <c r="BE5" s="110"/>
-      <c r="BF5" s="110"/>
-      <c r="BG5" s="110"/>
-      <c r="BH5" s="110"/>
-      <c r="BI5" s="110"/>
-      <c r="BJ5" s="110"/>
-      <c r="BK5" s="111"/>
+      <c r="BC5" s="114"/>
+      <c r="BD5" s="114"/>
+      <c r="BE5" s="114"/>
+      <c r="BF5" s="114"/>
+      <c r="BG5" s="114"/>
+      <c r="BH5" s="114"/>
+      <c r="BI5" s="114"/>
+      <c r="BJ5" s="114"/>
+      <c r="BK5" s="115"/>
     </row>
     <row r="6" spans="1:70" s="1" customFormat="1" ht="12" customHeight="1" thickBot="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="205"/>
-      <c r="J6" s="206"/>
-      <c r="K6" s="206"/>
-      <c r="L6" s="206"/>
-      <c r="M6" s="206"/>
-      <c r="N6" s="173"/>
-      <c r="O6" s="209"/>
-      <c r="P6" s="209"/>
-      <c r="Q6" s="209"/>
-      <c r="R6" s="209"/>
-      <c r="S6" s="209"/>
-      <c r="T6" s="209"/>
-      <c r="U6" s="209"/>
-      <c r="V6" s="209"/>
-      <c r="W6" s="209"/>
-      <c r="X6" s="209"/>
-      <c r="Y6" s="209"/>
-      <c r="Z6" s="209"/>
-      <c r="AA6" s="209"/>
-      <c r="AB6" s="209"/>
-      <c r="AC6" s="209"/>
-      <c r="AD6" s="209"/>
-      <c r="AE6" s="209"/>
-      <c r="AF6" s="209"/>
-      <c r="AG6" s="209"/>
-      <c r="AH6" s="209"/>
-      <c r="AI6" s="209"/>
-      <c r="AJ6" s="209"/>
-      <c r="AK6" s="209"/>
-      <c r="AL6" s="209"/>
-      <c r="AM6" s="209"/>
-      <c r="AN6" s="209"/>
-      <c r="AO6" s="209"/>
-      <c r="AP6" s="209"/>
-      <c r="AQ6" s="209"/>
-      <c r="AR6" s="210"/>
-      <c r="AS6" s="81" t="s">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="206"/>
+      <c r="J6" s="207"/>
+      <c r="K6" s="207"/>
+      <c r="L6" s="207"/>
+      <c r="M6" s="207"/>
+      <c r="N6" s="177"/>
+      <c r="O6" s="210"/>
+      <c r="P6" s="210"/>
+      <c r="Q6" s="210"/>
+      <c r="R6" s="210"/>
+      <c r="S6" s="210"/>
+      <c r="T6" s="210"/>
+      <c r="U6" s="210"/>
+      <c r="V6" s="210"/>
+      <c r="W6" s="210"/>
+      <c r="X6" s="210"/>
+      <c r="Y6" s="210"/>
+      <c r="Z6" s="210"/>
+      <c r="AA6" s="210"/>
+      <c r="AB6" s="210"/>
+      <c r="AC6" s="210"/>
+      <c r="AD6" s="210"/>
+      <c r="AE6" s="210"/>
+      <c r="AF6" s="210"/>
+      <c r="AG6" s="210"/>
+      <c r="AH6" s="210"/>
+      <c r="AI6" s="210"/>
+      <c r="AJ6" s="210"/>
+      <c r="AK6" s="210"/>
+      <c r="AL6" s="210"/>
+      <c r="AM6" s="210"/>
+      <c r="AN6" s="210"/>
+      <c r="AO6" s="210"/>
+      <c r="AP6" s="210"/>
+      <c r="AQ6" s="210"/>
+      <c r="AR6" s="211"/>
+      <c r="AS6" s="85" t="s">
         <v>8</v>
       </c>
-      <c r="AT6" s="82"/>
-      <c r="AU6" s="82"/>
-      <c r="AV6" s="82"/>
-      <c r="AW6" s="82"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="82"/>
-      <c r="AZ6" s="82"/>
-      <c r="BA6" s="24" t="s">
+      <c r="AT6" s="86"/>
+      <c r="AU6" s="86"/>
+      <c r="AV6" s="86"/>
+      <c r="AW6" s="86"/>
+      <c r="AX6" s="86"/>
+      <c r="AY6" s="86"/>
+      <c r="AZ6" s="86"/>
+      <c r="BA6" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="BB6" s="83"/>
-      <c r="BC6" s="83"/>
-      <c r="BD6" s="83"/>
-      <c r="BE6" s="83"/>
-      <c r="BF6" s="83"/>
-      <c r="BG6" s="83"/>
-      <c r="BH6" s="83"/>
-      <c r="BI6" s="83"/>
-      <c r="BJ6" s="83"/>
-      <c r="BK6" s="84"/>
+      <c r="BB6" s="87"/>
+      <c r="BC6" s="87"/>
+      <c r="BD6" s="87"/>
+      <c r="BE6" s="87"/>
+      <c r="BF6" s="87"/>
+      <c r="BG6" s="87"/>
+      <c r="BH6" s="87"/>
+      <c r="BI6" s="87"/>
+      <c r="BJ6" s="87"/>
+      <c r="BK6" s="88"/>
     </row>
     <row r="7" spans="1:70" ht="3.45" customHeight="1">
-      <c r="A7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="BK7" s="25"/>
+      <c r="A7" s="9"/>
+      <c r="I7" s="10"/>
+      <c r="BK7" s="21"/>
     </row>
     <row r="8" spans="1:70" ht="12.45" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="I8" s="26" t="s">
+      <c r="A8" s="9"/>
+      <c r="I8" s="22" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="85" t="s">
+      <c r="T8" s="89" t="s">
         <v>54</v>
       </c>
-      <c r="U8" s="85"/>
-      <c r="V8" s="85"/>
-      <c r="W8" s="85"/>
-      <c r="X8" s="85"/>
-      <c r="Y8" s="85"/>
-      <c r="Z8" s="85"/>
-      <c r="AA8" s="85"/>
-      <c r="AB8" s="85"/>
-      <c r="AC8" s="85"/>
-      <c r="AD8" s="85"/>
-      <c r="AE8" s="85"/>
-      <c r="AP8" s="27" t="s">
+      <c r="U8" s="89"/>
+      <c r="V8" s="89"/>
+      <c r="W8" s="89"/>
+      <c r="X8" s="89"/>
+      <c r="Y8" s="89"/>
+      <c r="Z8" s="89"/>
+      <c r="AA8" s="89"/>
+      <c r="AB8" s="89"/>
+      <c r="AC8" s="89"/>
+      <c r="AD8" s="89"/>
+      <c r="AE8" s="89"/>
+      <c r="AP8" s="23" t="s">
         <v>10</v>
       </c>
       <c r="AV8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AW8" s="86"/>
-      <c r="AX8" s="85"/>
-      <c r="AY8" s="85"/>
-      <c r="AZ8" s="85"/>
-      <c r="BA8" s="85"/>
-      <c r="BB8" s="85"/>
-      <c r="BC8" s="85"/>
-      <c r="BD8" s="85"/>
-      <c r="BE8" s="85"/>
-      <c r="BF8" s="85"/>
-      <c r="BG8" s="85"/>
-      <c r="BH8" s="85"/>
-      <c r="BK8" s="25"/>
+      <c r="AW8" s="90"/>
+      <c r="AX8" s="89"/>
+      <c r="AY8" s="89"/>
+      <c r="AZ8" s="89"/>
+      <c r="BA8" s="89"/>
+      <c r="BB8" s="89"/>
+      <c r="BC8" s="89"/>
+      <c r="BD8" s="89"/>
+      <c r="BE8" s="89"/>
+      <c r="BF8" s="89"/>
+      <c r="BG8" s="89"/>
+      <c r="BH8" s="89"/>
+      <c r="BK8" s="21"/>
     </row>
     <row r="9" spans="1:70" ht="12.45" customHeight="1">
-      <c r="A9" s="11"/>
-      <c r="I9" s="26" t="s">
+      <c r="A9" s="9"/>
+      <c r="I9" s="22" t="s">
         <v>12</v>
       </c>
       <c r="S9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="T9" s="87" t="s">
+      <c r="T9" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="U9" s="87"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="87"/>
-      <c r="X9" s="87"/>
-      <c r="Y9" s="87"/>
-      <c r="Z9" s="87"/>
-      <c r="AA9" s="87"/>
-      <c r="AB9" s="87"/>
-      <c r="AC9" s="87"/>
-      <c r="AD9" s="87"/>
-      <c r="AE9" s="87"/>
-      <c r="AP9" s="27" t="s">
+      <c r="U9" s="91"/>
+      <c r="V9" s="91"/>
+      <c r="W9" s="91"/>
+      <c r="X9" s="91"/>
+      <c r="Y9" s="91"/>
+      <c r="Z9" s="91"/>
+      <c r="AA9" s="91"/>
+      <c r="AB9" s="91"/>
+      <c r="AC9" s="91"/>
+      <c r="AD9" s="91"/>
+      <c r="AE9" s="91"/>
+      <c r="AP9" s="23" t="s">
         <v>13</v>
       </c>
       <c r="AV9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="AW9" s="88" t="s">
+      <c r="AW9" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="AX9" s="88"/>
-      <c r="AY9" s="88"/>
-      <c r="AZ9" s="88"/>
-      <c r="BA9" s="88"/>
-      <c r="BB9" s="88"/>
-      <c r="BC9" s="88"/>
-      <c r="BD9" s="88"/>
-      <c r="BE9" s="88"/>
-      <c r="BF9" s="88"/>
-      <c r="BG9" s="88"/>
-      <c r="BH9" s="88"/>
-      <c r="BK9" s="25"/>
+      <c r="AX9" s="92"/>
+      <c r="AY9" s="92"/>
+      <c r="AZ9" s="92"/>
+      <c r="BA9" s="92"/>
+      <c r="BB9" s="92"/>
+      <c r="BC9" s="92"/>
+      <c r="BD9" s="92"/>
+      <c r="BE9" s="92"/>
+      <c r="BF9" s="92"/>
+      <c r="BG9" s="92"/>
+      <c r="BH9" s="92"/>
+      <c r="BK9" s="21"/>
     </row>
     <row r="10" spans="1:70" ht="3.45" customHeight="1">
-      <c r="A10" s="11"/>
-      <c r="I10" s="12"/>
+      <c r="A10" s="9"/>
+      <c r="I10" s="10"/>
       <c r="T10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="BK10" s="25"/>
+      <c r="BK10" s="21"/>
     </row>
     <row r="11" spans="1:70" ht="13.95" customHeight="1">
-      <c r="A11" s="170" t="s">
+      <c r="A11" s="174" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="171" t="s">
+      <c r="B11" s="175" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="171" t="s">
+      <c r="C11" s="175" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="171" t="s">
+      <c r="D11" s="175" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="217" t="s">
+      <c r="I11" s="218" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="218"/>
-      <c r="K11" s="221" t="s">
+      <c r="J11" s="219"/>
+      <c r="K11" s="222" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="222"/>
-      <c r="M11" s="211" t="s">
+      <c r="L11" s="223"/>
+      <c r="M11" s="212" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="212"/>
-      <c r="O11" s="212"/>
-      <c r="P11" s="212"/>
-      <c r="Q11" s="212"/>
-      <c r="R11" s="212"/>
-      <c r="S11" s="212"/>
-      <c r="T11" s="212"/>
-      <c r="U11" s="212"/>
-      <c r="V11" s="212"/>
-      <c r="W11" s="212"/>
-      <c r="X11" s="212"/>
-      <c r="Y11" s="212"/>
-      <c r="Z11" s="212"/>
-      <c r="AA11" s="212"/>
-      <c r="AB11" s="212"/>
-      <c r="AC11" s="213"/>
-      <c r="AD11" s="89" t="s">
+      <c r="N11" s="213"/>
+      <c r="O11" s="213"/>
+      <c r="P11" s="213"/>
+      <c r="Q11" s="213"/>
+      <c r="R11" s="213"/>
+      <c r="S11" s="213"/>
+      <c r="T11" s="213"/>
+      <c r="U11" s="213"/>
+      <c r="V11" s="213"/>
+      <c r="W11" s="213"/>
+      <c r="X11" s="213"/>
+      <c r="Y11" s="213"/>
+      <c r="Z11" s="213"/>
+      <c r="AA11" s="213"/>
+      <c r="AB11" s="213"/>
+      <c r="AC11" s="214"/>
+      <c r="AD11" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="AE11" s="90"/>
-      <c r="AF11" s="90"/>
-      <c r="AG11" s="90"/>
-      <c r="AH11" s="90"/>
-      <c r="AI11" s="90"/>
-      <c r="AJ11" s="90"/>
-      <c r="AK11" s="90"/>
-      <c r="AL11" s="90"/>
-      <c r="AM11" s="90"/>
-      <c r="AN11" s="90"/>
-      <c r="AO11" s="91"/>
-      <c r="AP11" s="89" t="s">
+      <c r="AE11" s="94"/>
+      <c r="AF11" s="94"/>
+      <c r="AG11" s="94"/>
+      <c r="AH11" s="94"/>
+      <c r="AI11" s="94"/>
+      <c r="AJ11" s="94"/>
+      <c r="AK11" s="94"/>
+      <c r="AL11" s="94"/>
+      <c r="AM11" s="94"/>
+      <c r="AN11" s="94"/>
+      <c r="AO11" s="95"/>
+      <c r="AP11" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="AQ11" s="90"/>
-      <c r="AR11" s="90"/>
-      <c r="AS11" s="90"/>
-      <c r="AT11" s="90"/>
-      <c r="AU11" s="90"/>
-      <c r="AV11" s="90"/>
-      <c r="AW11" s="90"/>
-      <c r="AX11" s="90"/>
-      <c r="AY11" s="90"/>
-      <c r="AZ11" s="90"/>
-      <c r="BA11" s="91"/>
-      <c r="BB11" s="225" t="s">
+      <c r="AQ11" s="94"/>
+      <c r="AR11" s="94"/>
+      <c r="AS11" s="94"/>
+      <c r="AT11" s="94"/>
+      <c r="AU11" s="94"/>
+      <c r="AV11" s="94"/>
+      <c r="AW11" s="94"/>
+      <c r="AX11" s="94"/>
+      <c r="AY11" s="94"/>
+      <c r="AZ11" s="94"/>
+      <c r="BA11" s="95"/>
+      <c r="BB11" s="226" t="s">
         <v>24</v>
       </c>
-      <c r="BC11" s="90"/>
-      <c r="BD11" s="90"/>
-      <c r="BE11" s="90"/>
-      <c r="BF11" s="90"/>
-      <c r="BG11" s="90"/>
-      <c r="BH11" s="90"/>
-      <c r="BI11" s="90"/>
-      <c r="BJ11" s="90"/>
-      <c r="BK11" s="91"/>
-      <c r="BL11" s="174"/>
-      <c r="BM11" s="174"/>
-      <c r="BN11" s="174"/>
-      <c r="BO11" s="174"/>
-      <c r="BP11" s="193"/>
+      <c r="BC11" s="94"/>
+      <c r="BD11" s="94"/>
+      <c r="BE11" s="94"/>
+      <c r="BF11" s="94"/>
+      <c r="BG11" s="94"/>
+      <c r="BH11" s="94"/>
+      <c r="BI11" s="94"/>
+      <c r="BJ11" s="94"/>
+      <c r="BK11" s="95"/>
+      <c r="BL11" s="178"/>
+      <c r="BM11" s="178"/>
+      <c r="BN11" s="178"/>
+      <c r="BO11" s="178"/>
+      <c r="BP11" s="197"/>
     </row>
     <row r="12" spans="1:70" ht="12" customHeight="1">
-      <c r="A12" s="170"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="171"/>
-      <c r="D12" s="171"/>
+      <c r="A12" s="174"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="175"/>
+      <c r="D12" s="175"/>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
@@ -4581,1487 +4611,1487 @@
       <c r="H12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="219"/>
-      <c r="J12" s="220"/>
-      <c r="K12" s="223"/>
-      <c r="L12" s="224"/>
-      <c r="M12" s="214"/>
-      <c r="N12" s="215"/>
-      <c r="O12" s="215"/>
-      <c r="P12" s="215"/>
-      <c r="Q12" s="215"/>
-      <c r="R12" s="215"/>
-      <c r="S12" s="215"/>
-      <c r="T12" s="215"/>
-      <c r="U12" s="215"/>
-      <c r="V12" s="215"/>
-      <c r="W12" s="215"/>
-      <c r="X12" s="215"/>
-      <c r="Y12" s="215"/>
-      <c r="Z12" s="215"/>
-      <c r="AA12" s="215"/>
-      <c r="AB12" s="215"/>
-      <c r="AC12" s="216"/>
-      <c r="AD12" s="92" t="s">
+      <c r="I12" s="220"/>
+      <c r="J12" s="221"/>
+      <c r="K12" s="224"/>
+      <c r="L12" s="225"/>
+      <c r="M12" s="215"/>
+      <c r="N12" s="216"/>
+      <c r="O12" s="216"/>
+      <c r="P12" s="216"/>
+      <c r="Q12" s="216"/>
+      <c r="R12" s="216"/>
+      <c r="S12" s="216"/>
+      <c r="T12" s="216"/>
+      <c r="U12" s="216"/>
+      <c r="V12" s="216"/>
+      <c r="W12" s="216"/>
+      <c r="X12" s="216"/>
+      <c r="Y12" s="216"/>
+      <c r="Z12" s="216"/>
+      <c r="AA12" s="216"/>
+      <c r="AB12" s="216"/>
+      <c r="AC12" s="217"/>
+      <c r="AD12" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="AE12" s="93"/>
-      <c r="AF12" s="93"/>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93" t="s">
+      <c r="AE12" s="97"/>
+      <c r="AF12" s="97"/>
+      <c r="AG12" s="97"/>
+      <c r="AH12" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="93"/>
-      <c r="AL12" s="94" t="s">
+      <c r="AI12" s="97"/>
+      <c r="AJ12" s="97"/>
+      <c r="AK12" s="97"/>
+      <c r="AL12" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="AM12" s="94"/>
-      <c r="AN12" s="94"/>
-      <c r="AO12" s="95"/>
-      <c r="AP12" s="92" t="s">
+      <c r="AM12" s="98"/>
+      <c r="AN12" s="98"/>
+      <c r="AO12" s="99"/>
+      <c r="AP12" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="AQ12" s="93"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="93"/>
-      <c r="AT12" s="93" t="s">
+      <c r="AQ12" s="97"/>
+      <c r="AR12" s="97"/>
+      <c r="AS12" s="97"/>
+      <c r="AT12" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="AU12" s="93"/>
-      <c r="AV12" s="93"/>
-      <c r="AW12" s="93"/>
-      <c r="AX12" s="94" t="s">
+      <c r="AU12" s="97"/>
+      <c r="AV12" s="97"/>
+      <c r="AW12" s="97"/>
+      <c r="AX12" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="AY12" s="94"/>
-      <c r="AZ12" s="94"/>
-      <c r="BA12" s="95"/>
-      <c r="BB12" s="226"/>
-      <c r="BC12" s="227"/>
-      <c r="BD12" s="227"/>
-      <c r="BE12" s="227"/>
-      <c r="BF12" s="227"/>
-      <c r="BG12" s="227"/>
-      <c r="BH12" s="227"/>
-      <c r="BI12" s="227"/>
-      <c r="BJ12" s="227"/>
-      <c r="BK12" s="228"/>
-      <c r="BL12" s="174"/>
-      <c r="BM12" s="174"/>
-      <c r="BN12" s="174"/>
-      <c r="BO12" s="174"/>
-      <c r="BP12" s="193"/>
+      <c r="AY12" s="98"/>
+      <c r="AZ12" s="98"/>
+      <c r="BA12" s="99"/>
+      <c r="BB12" s="227"/>
+      <c r="BC12" s="228"/>
+      <c r="BD12" s="228"/>
+      <c r="BE12" s="228"/>
+      <c r="BF12" s="228"/>
+      <c r="BG12" s="228"/>
+      <c r="BH12" s="228"/>
+      <c r="BI12" s="228"/>
+      <c r="BJ12" s="228"/>
+      <c r="BK12" s="229"/>
+      <c r="BL12" s="178"/>
+      <c r="BM12" s="178"/>
+      <c r="BN12" s="178"/>
+      <c r="BO12" s="178"/>
+      <c r="BP12" s="197"/>
     </row>
     <row r="13" spans="1:70" ht="12.75" customHeight="1">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="115" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="116"/>
-      <c r="K13" s="117" t="s">
+      <c r="J13" s="120"/>
+      <c r="K13" s="121" t="s">
         <v>58</v>
       </c>
-      <c r="L13" s="118"/>
-      <c r="M13" s="119" t="s">
+      <c r="L13" s="122"/>
+      <c r="M13" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="120"/>
-      <c r="O13" s="120"/>
-      <c r="P13" s="120"/>
-      <c r="Q13" s="120"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="120"/>
-      <c r="U13" s="120"/>
-      <c r="V13" s="120"/>
-      <c r="W13" s="120"/>
-      <c r="X13" s="120"/>
-      <c r="Y13" s="120"/>
-      <c r="Z13" s="120"/>
-      <c r="AA13" s="120"/>
-      <c r="AB13" s="120"/>
-      <c r="AC13" s="121"/>
-      <c r="AD13" s="136"/>
-      <c r="AE13" s="137"/>
-      <c r="AF13" s="137"/>
-      <c r="AG13" s="138"/>
-      <c r="AH13" s="130"/>
-      <c r="AI13" s="131"/>
-      <c r="AJ13" s="131"/>
-      <c r="AK13" s="132"/>
-      <c r="AL13" s="133"/>
-      <c r="AM13" s="134"/>
-      <c r="AN13" s="134"/>
-      <c r="AO13" s="135"/>
-      <c r="AP13" s="127"/>
-      <c r="AQ13" s="128"/>
-      <c r="AR13" s="128"/>
-      <c r="AS13" s="129"/>
-      <c r="AT13" s="130"/>
-      <c r="AU13" s="131"/>
-      <c r="AV13" s="131"/>
-      <c r="AW13" s="132"/>
-      <c r="AX13" s="133"/>
-      <c r="AY13" s="134"/>
-      <c r="AZ13" s="134"/>
-      <c r="BA13" s="135"/>
-      <c r="BB13" s="112" t="s">
+      <c r="N13" s="124"/>
+      <c r="O13" s="124"/>
+      <c r="P13" s="124"/>
+      <c r="Q13" s="124"/>
+      <c r="R13" s="124"/>
+      <c r="S13" s="124"/>
+      <c r="T13" s="124"/>
+      <c r="U13" s="124"/>
+      <c r="V13" s="124"/>
+      <c r="W13" s="124"/>
+      <c r="X13" s="124"/>
+      <c r="Y13" s="124"/>
+      <c r="Z13" s="124"/>
+      <c r="AA13" s="124"/>
+      <c r="AB13" s="124"/>
+      <c r="AC13" s="125"/>
+      <c r="AD13" s="140"/>
+      <c r="AE13" s="141"/>
+      <c r="AF13" s="141"/>
+      <c r="AG13" s="142"/>
+      <c r="AH13" s="134"/>
+      <c r="AI13" s="135"/>
+      <c r="AJ13" s="135"/>
+      <c r="AK13" s="136"/>
+      <c r="AL13" s="137"/>
+      <c r="AM13" s="138"/>
+      <c r="AN13" s="138"/>
+      <c r="AO13" s="139"/>
+      <c r="AP13" s="131"/>
+      <c r="AQ13" s="132"/>
+      <c r="AR13" s="132"/>
+      <c r="AS13" s="133"/>
+      <c r="AT13" s="134"/>
+      <c r="AU13" s="135"/>
+      <c r="AV13" s="135"/>
+      <c r="AW13" s="136"/>
+      <c r="AX13" s="137"/>
+      <c r="AY13" s="138"/>
+      <c r="AZ13" s="138"/>
+      <c r="BA13" s="139"/>
+      <c r="BB13" s="116" t="s">
         <v>60</v>
       </c>
-      <c r="BC13" s="113"/>
-      <c r="BD13" s="113"/>
-      <c r="BE13" s="113"/>
-      <c r="BF13" s="113"/>
-      <c r="BG13" s="113"/>
-      <c r="BH13" s="113"/>
-      <c r="BI13" s="113"/>
-      <c r="BJ13" s="113"/>
-      <c r="BK13" s="114"/>
-      <c r="BL13" s="33"/>
-      <c r="BM13" s="34"/>
-      <c r="BN13" s="33"/>
-      <c r="BO13" s="33"/>
+      <c r="BC13" s="117"/>
+      <c r="BD13" s="117"/>
+      <c r="BE13" s="117"/>
+      <c r="BF13" s="117"/>
+      <c r="BG13" s="117"/>
+      <c r="BH13" s="117"/>
+      <c r="BI13" s="117"/>
+      <c r="BJ13" s="117"/>
+      <c r="BK13" s="118"/>
+      <c r="BL13" s="29"/>
+      <c r="BM13" s="30"/>
+      <c r="BN13" s="29"/>
+      <c r="BO13" s="29"/>
     </row>
     <row r="14" spans="1:70" ht="12.75" customHeight="1">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="119"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="120"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="120"/>
-      <c r="U14" s="120"/>
-      <c r="V14" s="120"/>
-      <c r="W14" s="120"/>
-      <c r="X14" s="120"/>
-      <c r="Y14" s="120"/>
-      <c r="Z14" s="120"/>
-      <c r="AA14" s="120"/>
-      <c r="AB14" s="120"/>
-      <c r="AC14" s="121"/>
-      <c r="AD14" s="130"/>
-      <c r="AE14" s="131"/>
-      <c r="AF14" s="131"/>
-      <c r="AG14" s="132"/>
-      <c r="AH14" s="130"/>
-      <c r="AI14" s="131"/>
-      <c r="AJ14" s="131"/>
-      <c r="AK14" s="132"/>
-      <c r="AL14" s="133"/>
-      <c r="AM14" s="134"/>
-      <c r="AN14" s="134"/>
-      <c r="AO14" s="135"/>
-      <c r="AP14" s="122"/>
-      <c r="AQ14" s="123"/>
-      <c r="AR14" s="123"/>
-      <c r="AS14" s="123"/>
-      <c r="AT14" s="124"/>
-      <c r="AU14" s="124"/>
-      <c r="AV14" s="124"/>
-      <c r="AW14" s="124"/>
-      <c r="AX14" s="125"/>
-      <c r="AY14" s="125"/>
-      <c r="AZ14" s="125"/>
-      <c r="BA14" s="126"/>
-      <c r="BB14" s="112"/>
-      <c r="BC14" s="113"/>
-      <c r="BD14" s="113"/>
-      <c r="BE14" s="113"/>
-      <c r="BF14" s="113"/>
-      <c r="BG14" s="113"/>
-      <c r="BH14" s="113"/>
-      <c r="BI14" s="113"/>
-      <c r="BJ14" s="113"/>
-      <c r="BK14" s="114"/>
-      <c r="BL14" s="33"/>
-      <c r="BM14" s="34"/>
-      <c r="BN14" s="33"/>
-      <c r="BO14" s="33"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="122"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="124"/>
+      <c r="O14" s="124"/>
+      <c r="P14" s="124"/>
+      <c r="Q14" s="124"/>
+      <c r="R14" s="124"/>
+      <c r="S14" s="124"/>
+      <c r="T14" s="124"/>
+      <c r="U14" s="124"/>
+      <c r="V14" s="124"/>
+      <c r="W14" s="124"/>
+      <c r="X14" s="124"/>
+      <c r="Y14" s="124"/>
+      <c r="Z14" s="124"/>
+      <c r="AA14" s="124"/>
+      <c r="AB14" s="124"/>
+      <c r="AC14" s="125"/>
+      <c r="AD14" s="134"/>
+      <c r="AE14" s="135"/>
+      <c r="AF14" s="135"/>
+      <c r="AG14" s="136"/>
+      <c r="AH14" s="134"/>
+      <c r="AI14" s="135"/>
+      <c r="AJ14" s="135"/>
+      <c r="AK14" s="136"/>
+      <c r="AL14" s="137"/>
+      <c r="AM14" s="138"/>
+      <c r="AN14" s="138"/>
+      <c r="AO14" s="139"/>
+      <c r="AP14" s="126"/>
+      <c r="AQ14" s="127"/>
+      <c r="AR14" s="127"/>
+      <c r="AS14" s="127"/>
+      <c r="AT14" s="128"/>
+      <c r="AU14" s="128"/>
+      <c r="AV14" s="128"/>
+      <c r="AW14" s="128"/>
+      <c r="AX14" s="129"/>
+      <c r="AY14" s="129"/>
+      <c r="AZ14" s="129"/>
+      <c r="BA14" s="130"/>
+      <c r="BB14" s="116"/>
+      <c r="BC14" s="117"/>
+      <c r="BD14" s="117"/>
+      <c r="BE14" s="117"/>
+      <c r="BF14" s="117"/>
+      <c r="BG14" s="117"/>
+      <c r="BH14" s="117"/>
+      <c r="BI14" s="117"/>
+      <c r="BJ14" s="117"/>
+      <c r="BK14" s="118"/>
+      <c r="BL14" s="29"/>
+      <c r="BM14" s="30"/>
+      <c r="BN14" s="29"/>
+      <c r="BO14" s="29"/>
     </row>
     <row r="15" spans="1:70" ht="12.75" customHeight="1">
-      <c r="A15" s="29"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="117"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="142"/>
-      <c r="O15" s="142"/>
-      <c r="P15" s="142"/>
-      <c r="Q15" s="142"/>
-      <c r="R15" s="142"/>
-      <c r="S15" s="142"/>
-      <c r="T15" s="142"/>
-      <c r="U15" s="142"/>
-      <c r="V15" s="142"/>
-      <c r="W15" s="142"/>
-      <c r="X15" s="142"/>
-      <c r="Y15" s="142"/>
-      <c r="Z15" s="142"/>
-      <c r="AA15" s="142"/>
-      <c r="AB15" s="142"/>
-      <c r="AC15" s="143"/>
-      <c r="AD15" s="130" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="145"/>
+      <c r="N15" s="146"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="146"/>
+      <c r="R15" s="146"/>
+      <c r="S15" s="146"/>
+      <c r="T15" s="146"/>
+      <c r="U15" s="146"/>
+      <c r="V15" s="146"/>
+      <c r="W15" s="146"/>
+      <c r="X15" s="146"/>
+      <c r="Y15" s="146"/>
+      <c r="Z15" s="146"/>
+      <c r="AA15" s="146"/>
+      <c r="AB15" s="146"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="AE15" s="131"/>
-      <c r="AF15" s="131"/>
-      <c r="AG15" s="132"/>
-      <c r="AH15" s="130"/>
-      <c r="AI15" s="131"/>
-      <c r="AJ15" s="131"/>
-      <c r="AK15" s="132"/>
-      <c r="AL15" s="133"/>
-      <c r="AM15" s="134"/>
-      <c r="AN15" s="134"/>
-      <c r="AO15" s="135"/>
-      <c r="AP15" s="127"/>
-      <c r="AQ15" s="128"/>
-      <c r="AR15" s="128"/>
-      <c r="AS15" s="129"/>
-      <c r="AT15" s="130"/>
-      <c r="AU15" s="131"/>
-      <c r="AV15" s="131"/>
-      <c r="AW15" s="132"/>
-      <c r="AX15" s="133"/>
-      <c r="AY15" s="134"/>
-      <c r="AZ15" s="134"/>
-      <c r="BA15" s="135"/>
-      <c r="BB15" s="139"/>
-      <c r="BC15" s="139"/>
-      <c r="BD15" s="139"/>
-      <c r="BE15" s="139"/>
-      <c r="BF15" s="139"/>
-      <c r="BG15" s="139"/>
-      <c r="BH15" s="139"/>
-      <c r="BI15" s="139"/>
-      <c r="BJ15" s="139"/>
-      <c r="BK15" s="140"/>
-      <c r="BL15" s="33"/>
-      <c r="BM15" s="34"/>
-      <c r="BN15" s="33"/>
-      <c r="BO15" s="33"/>
-      <c r="BQ15" s="35"/>
-      <c r="BR15" s="12"/>
+      <c r="AE15" s="135"/>
+      <c r="AF15" s="135"/>
+      <c r="AG15" s="136"/>
+      <c r="AH15" s="134"/>
+      <c r="AI15" s="135"/>
+      <c r="AJ15" s="135"/>
+      <c r="AK15" s="136"/>
+      <c r="AL15" s="137"/>
+      <c r="AM15" s="138"/>
+      <c r="AN15" s="138"/>
+      <c r="AO15" s="139"/>
+      <c r="AP15" s="131"/>
+      <c r="AQ15" s="132"/>
+      <c r="AR15" s="132"/>
+      <c r="AS15" s="133"/>
+      <c r="AT15" s="134"/>
+      <c r="AU15" s="135"/>
+      <c r="AV15" s="135"/>
+      <c r="AW15" s="136"/>
+      <c r="AX15" s="137"/>
+      <c r="AY15" s="138"/>
+      <c r="AZ15" s="138"/>
+      <c r="BA15" s="139"/>
+      <c r="BB15" s="143"/>
+      <c r="BC15" s="143"/>
+      <c r="BD15" s="143"/>
+      <c r="BE15" s="143"/>
+      <c r="BF15" s="143"/>
+      <c r="BG15" s="143"/>
+      <c r="BH15" s="143"/>
+      <c r="BI15" s="143"/>
+      <c r="BJ15" s="143"/>
+      <c r="BK15" s="144"/>
+      <c r="BL15" s="29"/>
+      <c r="BM15" s="30"/>
+      <c r="BN15" s="29"/>
+      <c r="BO15" s="29"/>
+      <c r="BQ15"/>
+      <c r="BR15"/>
     </row>
     <row r="16" spans="1:70" ht="12.75" customHeight="1">
-      <c r="A16" s="29" t="str">
+      <c r="A16" s="25" t="str">
         <f t="shared" ref="A16:A24" si="0">IF(I16&lt;&gt;"",$BB$6,"")</f>
         <v/>
       </c>
-      <c r="B16" s="30" t="str">
+      <c r="B16" s="26" t="str">
         <f t="shared" ref="B16:B24" si="1">IF(I16&lt;&gt;"",$T$9,"")</f>
         <v/>
       </c>
-      <c r="C16" s="31" t="str">
+      <c r="C16" s="27" t="str">
         <f t="shared" ref="C16:C24" si="2">IF(I16&lt;&gt;"",$AW$9,"")</f>
         <v/>
       </c>
-      <c r="D16" s="31" t="str">
+      <c r="D16" s="27" t="str">
         <f t="shared" ref="D16:D24" si="3">IF(I16&lt;&gt;"",$I$26,"")</f>
         <v/>
       </c>
-      <c r="E16" s="31" t="str">
+      <c r="E16" s="27" t="str">
         <f t="shared" ref="E16:E24" si="4">IF(I16&lt;&gt;"",I16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="31" t="str">
+      <c r="F16" s="27" t="str">
         <f t="shared" ref="F16:F24" si="5">IF(I16&lt;&gt;"",K16,"")</f>
         <v/>
       </c>
-      <c r="G16" s="31" t="str">
+      <c r="G16" s="27" t="str">
         <f>IF(I16&lt;&gt;"",M18,"")</f>
         <v/>
       </c>
-      <c r="H16" s="77" t="str">
+      <c r="H16" s="72" t="str">
         <f t="shared" ref="H16:H24" si="6">IF(I16&lt;&gt;"",$AW$8,"")</f>
         <v/>
       </c>
-      <c r="I16" s="115"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="142"/>
-      <c r="O16" s="142"/>
-      <c r="P16" s="142"/>
-      <c r="Q16" s="142"/>
-      <c r="R16" s="142"/>
-      <c r="S16" s="142"/>
-      <c r="T16" s="142"/>
-      <c r="U16" s="142"/>
-      <c r="V16" s="142"/>
-      <c r="W16" s="142"/>
-      <c r="X16" s="142"/>
-      <c r="Y16" s="142"/>
-      <c r="Z16" s="142"/>
-      <c r="AA16" s="142"/>
-      <c r="AB16" s="142"/>
-      <c r="AC16" s="143"/>
-      <c r="AD16" s="130"/>
-      <c r="AE16" s="131"/>
-      <c r="AF16" s="131"/>
-      <c r="AG16" s="132"/>
-      <c r="AH16" s="124"/>
-      <c r="AI16" s="124"/>
-      <c r="AJ16" s="124"/>
-      <c r="AK16" s="124"/>
-      <c r="AL16" s="125"/>
-      <c r="AM16" s="125"/>
-      <c r="AN16" s="125"/>
-      <c r="AO16" s="126"/>
-      <c r="AP16" s="122"/>
-      <c r="AQ16" s="123"/>
-      <c r="AR16" s="123"/>
-      <c r="AS16" s="123"/>
-      <c r="AT16" s="124"/>
-      <c r="AU16" s="124"/>
-      <c r="AV16" s="124"/>
-      <c r="AW16" s="124"/>
-      <c r="AX16" s="125"/>
-      <c r="AY16" s="125"/>
-      <c r="AZ16" s="125"/>
-      <c r="BA16" s="133"/>
-      <c r="BB16" s="144"/>
-      <c r="BC16" s="139"/>
-      <c r="BD16" s="139"/>
-      <c r="BE16" s="139"/>
-      <c r="BF16" s="139"/>
-      <c r="BG16" s="139"/>
-      <c r="BH16" s="139"/>
-      <c r="BI16" s="139"/>
-      <c r="BJ16" s="139"/>
-      <c r="BK16" s="140"/>
-      <c r="BL16" s="33"/>
-      <c r="BM16" s="34"/>
-      <c r="BN16" s="33"/>
-      <c r="BO16" s="33"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="122"/>
+      <c r="M16" s="145"/>
+      <c r="N16" s="146"/>
+      <c r="O16" s="146"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="146"/>
+      <c r="R16" s="146"/>
+      <c r="S16" s="146"/>
+      <c r="T16" s="146"/>
+      <c r="U16" s="146"/>
+      <c r="V16" s="146"/>
+      <c r="W16" s="146"/>
+      <c r="X16" s="146"/>
+      <c r="Y16" s="146"/>
+      <c r="Z16" s="146"/>
+      <c r="AA16" s="146"/>
+      <c r="AB16" s="146"/>
+      <c r="AC16" s="147"/>
+      <c r="AD16" s="134"/>
+      <c r="AE16" s="135"/>
+      <c r="AF16" s="135"/>
+      <c r="AG16" s="136"/>
+      <c r="AH16" s="128"/>
+      <c r="AI16" s="128"/>
+      <c r="AJ16" s="128"/>
+      <c r="AK16" s="128"/>
+      <c r="AL16" s="129"/>
+      <c r="AM16" s="129"/>
+      <c r="AN16" s="129"/>
+      <c r="AO16" s="130"/>
+      <c r="AP16" s="126"/>
+      <c r="AQ16" s="127"/>
+      <c r="AR16" s="127"/>
+      <c r="AS16" s="127"/>
+      <c r="AT16" s="128"/>
+      <c r="AU16" s="128"/>
+      <c r="AV16" s="128"/>
+      <c r="AW16" s="128"/>
+      <c r="AX16" s="129"/>
+      <c r="AY16" s="129"/>
+      <c r="AZ16" s="129"/>
+      <c r="BA16" s="137"/>
+      <c r="BB16" s="148"/>
+      <c r="BC16" s="143"/>
+      <c r="BD16" s="143"/>
+      <c r="BE16" s="143"/>
+      <c r="BF16" s="143"/>
+      <c r="BG16" s="143"/>
+      <c r="BH16" s="143"/>
+      <c r="BI16" s="143"/>
+      <c r="BJ16" s="143"/>
+      <c r="BK16" s="144"/>
+      <c r="BL16" s="29"/>
+      <c r="BM16" s="30"/>
+      <c r="BN16" s="29"/>
+      <c r="BO16" s="29"/>
     </row>
     <row r="17" spans="1:68" ht="12.75" customHeight="1">
-      <c r="A17" s="29" t="str">
+      <c r="A17" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B17" s="30" t="str">
+      <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C17" s="31" t="str">
+      <c r="C17" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="D17" s="31" t="str">
+      <c r="D17" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="E17" s="31" t="str">
+      <c r="E17" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F17" s="31" t="str">
+      <c r="F17" s="27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G17" s="31" t="str">
+      <c r="G17" s="27" t="str">
         <f>IF(I17&lt;&gt;"",#REF!,"")</f>
         <v/>
       </c>
-      <c r="H17" s="77" t="str">
+      <c r="H17" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="I17" s="115"/>
-      <c r="J17" s="116"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="142"/>
-      <c r="O17" s="142"/>
-      <c r="P17" s="142"/>
-      <c r="Q17" s="142"/>
-      <c r="R17" s="142"/>
-      <c r="S17" s="142"/>
-      <c r="T17" s="142"/>
-      <c r="U17" s="142"/>
-      <c r="V17" s="142"/>
-      <c r="W17" s="142"/>
-      <c r="X17" s="142"/>
-      <c r="Y17" s="142"/>
-      <c r="Z17" s="142"/>
-      <c r="AA17" s="142"/>
-      <c r="AB17" s="142"/>
-      <c r="AC17" s="143"/>
-      <c r="AD17" s="122"/>
-      <c r="AE17" s="123"/>
-      <c r="AF17" s="123"/>
-      <c r="AG17" s="123"/>
-      <c r="AH17" s="124"/>
-      <c r="AI17" s="124"/>
-      <c r="AJ17" s="124"/>
-      <c r="AK17" s="124"/>
-      <c r="AL17" s="125"/>
-      <c r="AM17" s="125"/>
-      <c r="AN17" s="125"/>
-      <c r="AO17" s="126"/>
-      <c r="AP17" s="122"/>
-      <c r="AQ17" s="123"/>
-      <c r="AR17" s="123"/>
-      <c r="AS17" s="123"/>
-      <c r="AT17" s="124"/>
-      <c r="AU17" s="124"/>
-      <c r="AV17" s="124"/>
-      <c r="AW17" s="124"/>
-      <c r="AX17" s="125"/>
-      <c r="AY17" s="125"/>
-      <c r="AZ17" s="125"/>
-      <c r="BA17" s="133"/>
-      <c r="BB17" s="144"/>
-      <c r="BC17" s="139"/>
-      <c r="BD17" s="139"/>
-      <c r="BE17" s="139"/>
-      <c r="BF17" s="139"/>
-      <c r="BG17" s="139"/>
-      <c r="BH17" s="139"/>
-      <c r="BI17" s="139"/>
-      <c r="BJ17" s="139"/>
-      <c r="BK17" s="140"/>
-      <c r="BL17" s="33"/>
-      <c r="BM17" s="34"/>
-      <c r="BN17" s="33"/>
-      <c r="BO17" s="33"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="120"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="145"/>
+      <c r="N17" s="146"/>
+      <c r="O17" s="146"/>
+      <c r="P17" s="146"/>
+      <c r="Q17" s="146"/>
+      <c r="R17" s="146"/>
+      <c r="S17" s="146"/>
+      <c r="T17" s="146"/>
+      <c r="U17" s="146"/>
+      <c r="V17" s="146"/>
+      <c r="W17" s="146"/>
+      <c r="X17" s="146"/>
+      <c r="Y17" s="146"/>
+      <c r="Z17" s="146"/>
+      <c r="AA17" s="146"/>
+      <c r="AB17" s="146"/>
+      <c r="AC17" s="147"/>
+      <c r="AD17" s="126"/>
+      <c r="AE17" s="127"/>
+      <c r="AF17" s="127"/>
+      <c r="AG17" s="127"/>
+      <c r="AH17" s="128"/>
+      <c r="AI17" s="128"/>
+      <c r="AJ17" s="128"/>
+      <c r="AK17" s="128"/>
+      <c r="AL17" s="129"/>
+      <c r="AM17" s="129"/>
+      <c r="AN17" s="129"/>
+      <c r="AO17" s="130"/>
+      <c r="AP17" s="126"/>
+      <c r="AQ17" s="127"/>
+      <c r="AR17" s="127"/>
+      <c r="AS17" s="127"/>
+      <c r="AT17" s="128"/>
+      <c r="AU17" s="128"/>
+      <c r="AV17" s="128"/>
+      <c r="AW17" s="128"/>
+      <c r="AX17" s="129"/>
+      <c r="AY17" s="129"/>
+      <c r="AZ17" s="129"/>
+      <c r="BA17" s="137"/>
+      <c r="BB17" s="148"/>
+      <c r="BC17" s="143"/>
+      <c r="BD17" s="143"/>
+      <c r="BE17" s="143"/>
+      <c r="BF17" s="143"/>
+      <c r="BG17" s="143"/>
+      <c r="BH17" s="143"/>
+      <c r="BI17" s="143"/>
+      <c r="BJ17" s="143"/>
+      <c r="BK17" s="144"/>
+      <c r="BL17" s="29"/>
+      <c r="BM17" s="30"/>
+      <c r="BN17" s="29"/>
+      <c r="BO17" s="29"/>
     </row>
     <row r="18" spans="1:68" ht="13.2">
-      <c r="A18" s="29" t="str">
+      <c r="A18" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B18" s="30" t="str">
+      <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C18" s="31" t="str">
+      <c r="C18" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="D18" s="31" t="str">
+      <c r="D18" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="E18" s="31" t="str">
+      <c r="E18" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F18" s="31" t="str">
+      <c r="F18" s="27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G18" s="31" t="str">
+      <c r="G18" s="27" t="str">
         <f>IF(I18&lt;&gt;"",#REF!,"")</f>
         <v/>
       </c>
-      <c r="H18" s="77" t="str">
+      <c r="H18" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="I18" s="115"/>
-      <c r="J18" s="116"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="145"/>
-      <c r="N18" s="146"/>
-      <c r="O18" s="146"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="146"/>
-      <c r="R18" s="146"/>
-      <c r="S18" s="146"/>
-      <c r="T18" s="146"/>
-      <c r="U18" s="146"/>
-      <c r="V18" s="146"/>
-      <c r="W18" s="146"/>
-      <c r="X18" s="146"/>
-      <c r="Y18" s="146"/>
-      <c r="Z18" s="146"/>
-      <c r="AA18" s="146"/>
-      <c r="AB18" s="146"/>
-      <c r="AC18" s="147"/>
-      <c r="AD18" s="122"/>
-      <c r="AE18" s="123"/>
-      <c r="AF18" s="123"/>
-      <c r="AG18" s="123"/>
-      <c r="AH18" s="124"/>
-      <c r="AI18" s="124"/>
-      <c r="AJ18" s="124"/>
-      <c r="AK18" s="124"/>
-      <c r="AL18" s="125"/>
-      <c r="AM18" s="125"/>
-      <c r="AN18" s="125"/>
-      <c r="AO18" s="126"/>
-      <c r="AP18" s="122"/>
-      <c r="AQ18" s="123"/>
-      <c r="AR18" s="123"/>
-      <c r="AS18" s="123"/>
-      <c r="AT18" s="124"/>
-      <c r="AU18" s="124"/>
-      <c r="AV18" s="124"/>
-      <c r="AW18" s="124"/>
-      <c r="AX18" s="125"/>
-      <c r="AY18" s="125"/>
-      <c r="AZ18" s="125"/>
-      <c r="BA18" s="133"/>
-      <c r="BB18" s="144"/>
-      <c r="BC18" s="139"/>
-      <c r="BD18" s="139"/>
-      <c r="BE18" s="139"/>
-      <c r="BF18" s="139"/>
-      <c r="BG18" s="139"/>
-      <c r="BH18" s="139"/>
-      <c r="BI18" s="139"/>
-      <c r="BJ18" s="139"/>
-      <c r="BK18" s="140"/>
-      <c r="BL18" s="33"/>
-      <c r="BM18" s="34"/>
-      <c r="BN18" s="33"/>
-      <c r="BO18" s="33"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="149"/>
+      <c r="N18" s="150"/>
+      <c r="O18" s="150"/>
+      <c r="P18" s="150"/>
+      <c r="Q18" s="150"/>
+      <c r="R18" s="150"/>
+      <c r="S18" s="150"/>
+      <c r="T18" s="150"/>
+      <c r="U18" s="150"/>
+      <c r="V18" s="150"/>
+      <c r="W18" s="150"/>
+      <c r="X18" s="150"/>
+      <c r="Y18" s="150"/>
+      <c r="Z18" s="150"/>
+      <c r="AA18" s="150"/>
+      <c r="AB18" s="150"/>
+      <c r="AC18" s="151"/>
+      <c r="AD18" s="126"/>
+      <c r="AE18" s="127"/>
+      <c r="AF18" s="127"/>
+      <c r="AG18" s="127"/>
+      <c r="AH18" s="128"/>
+      <c r="AI18" s="128"/>
+      <c r="AJ18" s="128"/>
+      <c r="AK18" s="128"/>
+      <c r="AL18" s="129"/>
+      <c r="AM18" s="129"/>
+      <c r="AN18" s="129"/>
+      <c r="AO18" s="130"/>
+      <c r="AP18" s="126"/>
+      <c r="AQ18" s="127"/>
+      <c r="AR18" s="127"/>
+      <c r="AS18" s="127"/>
+      <c r="AT18" s="128"/>
+      <c r="AU18" s="128"/>
+      <c r="AV18" s="128"/>
+      <c r="AW18" s="128"/>
+      <c r="AX18" s="129"/>
+      <c r="AY18" s="129"/>
+      <c r="AZ18" s="129"/>
+      <c r="BA18" s="137"/>
+      <c r="BB18" s="148"/>
+      <c r="BC18" s="143"/>
+      <c r="BD18" s="143"/>
+      <c r="BE18" s="143"/>
+      <c r="BF18" s="143"/>
+      <c r="BG18" s="143"/>
+      <c r="BH18" s="143"/>
+      <c r="BI18" s="143"/>
+      <c r="BJ18" s="143"/>
+      <c r="BK18" s="144"/>
+      <c r="BL18" s="29"/>
+      <c r="BM18" s="30"/>
+      <c r="BN18" s="29"/>
+      <c r="BO18" s="29"/>
     </row>
     <row r="19" spans="1:68" ht="13.2">
-      <c r="A19" s="29"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="145"/>
-      <c r="N19" s="146"/>
-      <c r="O19" s="146"/>
-      <c r="P19" s="146"/>
-      <c r="Q19" s="146"/>
-      <c r="R19" s="146"/>
-      <c r="S19" s="146"/>
-      <c r="T19" s="146"/>
-      <c r="U19" s="146"/>
-      <c r="V19" s="146"/>
-      <c r="W19" s="146"/>
-      <c r="X19" s="146"/>
-      <c r="Y19" s="146"/>
-      <c r="Z19" s="146"/>
-      <c r="AA19" s="146"/>
-      <c r="AB19" s="146"/>
-      <c r="AC19" s="147"/>
-      <c r="AD19" s="122"/>
-      <c r="AE19" s="123"/>
-      <c r="AF19" s="123"/>
-      <c r="AG19" s="123"/>
-      <c r="AH19" s="124"/>
-      <c r="AI19" s="124"/>
-      <c r="AJ19" s="124"/>
-      <c r="AK19" s="124"/>
-      <c r="AL19" s="125"/>
-      <c r="AM19" s="125"/>
-      <c r="AN19" s="125"/>
-      <c r="AO19" s="126"/>
-      <c r="AP19" s="122"/>
-      <c r="AQ19" s="123"/>
-      <c r="AR19" s="123"/>
-      <c r="AS19" s="123"/>
-      <c r="AT19" s="124"/>
-      <c r="AU19" s="124"/>
-      <c r="AV19" s="124"/>
-      <c r="AW19" s="124"/>
-      <c r="AX19" s="125"/>
-      <c r="AY19" s="125"/>
-      <c r="AZ19" s="125"/>
-      <c r="BA19" s="126"/>
-      <c r="BB19" s="148"/>
-      <c r="BC19" s="149"/>
-      <c r="BD19" s="149"/>
-      <c r="BE19" s="149"/>
-      <c r="BF19" s="149"/>
-      <c r="BG19" s="149"/>
-      <c r="BH19" s="149"/>
-      <c r="BI19" s="149"/>
-      <c r="BJ19" s="149"/>
-      <c r="BK19" s="150"/>
-      <c r="BL19" s="33"/>
-      <c r="BM19" s="34"/>
-      <c r="BN19" s="33"/>
-      <c r="BO19" s="33"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="120"/>
+      <c r="K19" s="121"/>
+      <c r="L19" s="122"/>
+      <c r="M19" s="149"/>
+      <c r="N19" s="150"/>
+      <c r="O19" s="150"/>
+      <c r="P19" s="150"/>
+      <c r="Q19" s="150"/>
+      <c r="R19" s="150"/>
+      <c r="S19" s="150"/>
+      <c r="T19" s="150"/>
+      <c r="U19" s="150"/>
+      <c r="V19" s="150"/>
+      <c r="W19" s="150"/>
+      <c r="X19" s="150"/>
+      <c r="Y19" s="150"/>
+      <c r="Z19" s="150"/>
+      <c r="AA19" s="150"/>
+      <c r="AB19" s="150"/>
+      <c r="AC19" s="151"/>
+      <c r="AD19" s="126"/>
+      <c r="AE19" s="127"/>
+      <c r="AF19" s="127"/>
+      <c r="AG19" s="127"/>
+      <c r="AH19" s="128"/>
+      <c r="AI19" s="128"/>
+      <c r="AJ19" s="128"/>
+      <c r="AK19" s="128"/>
+      <c r="AL19" s="129"/>
+      <c r="AM19" s="129"/>
+      <c r="AN19" s="129"/>
+      <c r="AO19" s="130"/>
+      <c r="AP19" s="126"/>
+      <c r="AQ19" s="127"/>
+      <c r="AR19" s="127"/>
+      <c r="AS19" s="127"/>
+      <c r="AT19" s="128"/>
+      <c r="AU19" s="128"/>
+      <c r="AV19" s="128"/>
+      <c r="AW19" s="128"/>
+      <c r="AX19" s="129"/>
+      <c r="AY19" s="129"/>
+      <c r="AZ19" s="129"/>
+      <c r="BA19" s="130"/>
+      <c r="BB19" s="152"/>
+      <c r="BC19" s="153"/>
+      <c r="BD19" s="153"/>
+      <c r="BE19" s="153"/>
+      <c r="BF19" s="153"/>
+      <c r="BG19" s="153"/>
+      <c r="BH19" s="153"/>
+      <c r="BI19" s="153"/>
+      <c r="BJ19" s="153"/>
+      <c r="BK19" s="154"/>
+      <c r="BL19" s="29"/>
+      <c r="BM19" s="30"/>
+      <c r="BN19" s="29"/>
+      <c r="BO19" s="29"/>
     </row>
     <row r="20" spans="1:68" ht="13.2">
-      <c r="A20" s="29"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="145"/>
-      <c r="N20" s="146"/>
-      <c r="O20" s="146"/>
-      <c r="P20" s="146"/>
-      <c r="Q20" s="146"/>
-      <c r="R20" s="146"/>
-      <c r="S20" s="146"/>
-      <c r="T20" s="146"/>
-      <c r="U20" s="146"/>
-      <c r="V20" s="146"/>
-      <c r="W20" s="146"/>
-      <c r="X20" s="146"/>
-      <c r="Y20" s="146"/>
-      <c r="Z20" s="146"/>
-      <c r="AA20" s="146"/>
-      <c r="AB20" s="146"/>
-      <c r="AC20" s="147"/>
-      <c r="AD20" s="127"/>
-      <c r="AE20" s="128"/>
-      <c r="AF20" s="128"/>
-      <c r="AG20" s="129"/>
-      <c r="AH20" s="130"/>
-      <c r="AI20" s="131"/>
-      <c r="AJ20" s="131"/>
-      <c r="AK20" s="132"/>
-      <c r="AL20" s="133"/>
-      <c r="AM20" s="134"/>
-      <c r="AN20" s="134"/>
-      <c r="AO20" s="135"/>
-      <c r="AP20" s="127"/>
-      <c r="AQ20" s="128"/>
-      <c r="AR20" s="128"/>
-      <c r="AS20" s="129"/>
-      <c r="AT20" s="130"/>
-      <c r="AU20" s="131"/>
-      <c r="AV20" s="131"/>
-      <c r="AW20" s="132"/>
-      <c r="AX20" s="133"/>
-      <c r="AY20" s="134"/>
-      <c r="AZ20" s="134"/>
-      <c r="BA20" s="135"/>
-      <c r="BB20" s="151"/>
-      <c r="BC20" s="152"/>
-      <c r="BD20" s="152"/>
-      <c r="BE20" s="152"/>
-      <c r="BF20" s="152"/>
-      <c r="BG20" s="152"/>
-      <c r="BH20" s="152"/>
-      <c r="BI20" s="152"/>
-      <c r="BJ20" s="152"/>
-      <c r="BK20" s="153"/>
-      <c r="BL20" s="33"/>
-      <c r="BM20" s="34"/>
-      <c r="BN20" s="33"/>
-      <c r="BO20" s="33"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="121"/>
+      <c r="L20" s="122"/>
+      <c r="M20" s="149"/>
+      <c r="N20" s="150"/>
+      <c r="O20" s="150"/>
+      <c r="P20" s="150"/>
+      <c r="Q20" s="150"/>
+      <c r="R20" s="150"/>
+      <c r="S20" s="150"/>
+      <c r="T20" s="150"/>
+      <c r="U20" s="150"/>
+      <c r="V20" s="150"/>
+      <c r="W20" s="150"/>
+      <c r="X20" s="150"/>
+      <c r="Y20" s="150"/>
+      <c r="Z20" s="150"/>
+      <c r="AA20" s="150"/>
+      <c r="AB20" s="150"/>
+      <c r="AC20" s="151"/>
+      <c r="AD20" s="131"/>
+      <c r="AE20" s="132"/>
+      <c r="AF20" s="132"/>
+      <c r="AG20" s="133"/>
+      <c r="AH20" s="134"/>
+      <c r="AI20" s="135"/>
+      <c r="AJ20" s="135"/>
+      <c r="AK20" s="136"/>
+      <c r="AL20" s="137"/>
+      <c r="AM20" s="138"/>
+      <c r="AN20" s="138"/>
+      <c r="AO20" s="139"/>
+      <c r="AP20" s="131"/>
+      <c r="AQ20" s="132"/>
+      <c r="AR20" s="132"/>
+      <c r="AS20" s="133"/>
+      <c r="AT20" s="134"/>
+      <c r="AU20" s="135"/>
+      <c r="AV20" s="135"/>
+      <c r="AW20" s="136"/>
+      <c r="AX20" s="137"/>
+      <c r="AY20" s="138"/>
+      <c r="AZ20" s="138"/>
+      <c r="BA20" s="139"/>
+      <c r="BB20" s="155"/>
+      <c r="BC20" s="156"/>
+      <c r="BD20" s="156"/>
+      <c r="BE20" s="156"/>
+      <c r="BF20" s="156"/>
+      <c r="BG20" s="156"/>
+      <c r="BH20" s="156"/>
+      <c r="BI20" s="156"/>
+      <c r="BJ20" s="156"/>
+      <c r="BK20" s="157"/>
+      <c r="BL20" s="29"/>
+      <c r="BM20" s="30"/>
+      <c r="BN20" s="29"/>
+      <c r="BO20" s="29"/>
     </row>
     <row r="21" spans="1:68" ht="13.2">
-      <c r="A21" s="29" t="str">
+      <c r="A21" s="25" t="str">
         <f t="shared" ref="A21:A23" si="7">IF(I21&lt;&gt;"",$BB$6,"")</f>
         <v/>
       </c>
-      <c r="B21" s="30" t="str">
+      <c r="B21" s="26" t="str">
         <f t="shared" ref="B21:B23" si="8">IF(I21&lt;&gt;"",$T$9,"")</f>
         <v/>
       </c>
-      <c r="C21" s="31" t="str">
+      <c r="C21" s="27" t="str">
         <f t="shared" ref="C21:C23" si="9">IF(I21&lt;&gt;"",$AW$9,"")</f>
         <v/>
       </c>
-      <c r="D21" s="31" t="str">
+      <c r="D21" s="27" t="str">
         <f t="shared" ref="D21:D23" si="10">IF(I21&lt;&gt;"",$I$26,"")</f>
         <v/>
       </c>
-      <c r="E21" s="31" t="str">
+      <c r="E21" s="27" t="str">
         <f t="shared" ref="E21:E23" si="11">IF(I21&lt;&gt;"",I21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="31" t="str">
+      <c r="F21" s="27" t="str">
         <f t="shared" ref="F21:F23" si="12">IF(I21&lt;&gt;"",K21,"")</f>
         <v/>
       </c>
-      <c r="G21" s="31" t="str">
+      <c r="G21" s="27" t="str">
         <f>IF(I21&lt;&gt;"",#REF!,"")</f>
         <v/>
       </c>
-      <c r="H21" s="77" t="str">
+      <c r="H21" s="72" t="str">
         <f t="shared" ref="H21:H23" si="13">IF(I21&lt;&gt;"",$AW$8,"")</f>
         <v/>
       </c>
-      <c r="I21" s="115"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="117"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="161"/>
-      <c r="N21" s="162"/>
-      <c r="O21" s="162"/>
-      <c r="P21" s="162"/>
-      <c r="Q21" s="162"/>
-      <c r="R21" s="162"/>
-      <c r="S21" s="162"/>
-      <c r="T21" s="162"/>
-      <c r="U21" s="162"/>
-      <c r="V21" s="162"/>
-      <c r="W21" s="162"/>
-      <c r="X21" s="162"/>
-      <c r="Y21" s="162"/>
-      <c r="Z21" s="162"/>
-      <c r="AA21" s="162"/>
-      <c r="AB21" s="162"/>
-      <c r="AC21" s="163"/>
-      <c r="AD21" s="127"/>
-      <c r="AE21" s="128"/>
-      <c r="AF21" s="128"/>
-      <c r="AG21" s="129"/>
-      <c r="AH21" s="130"/>
-      <c r="AI21" s="131"/>
-      <c r="AJ21" s="131"/>
-      <c r="AK21" s="132"/>
-      <c r="AL21" s="133"/>
-      <c r="AM21" s="134"/>
-      <c r="AN21" s="134"/>
-      <c r="AO21" s="135"/>
-      <c r="AP21" s="127"/>
-      <c r="AQ21" s="128"/>
-      <c r="AR21" s="128"/>
-      <c r="AS21" s="129"/>
-      <c r="AT21" s="130"/>
-      <c r="AU21" s="131"/>
-      <c r="AV21" s="131"/>
-      <c r="AW21" s="132"/>
-      <c r="AX21" s="133"/>
-      <c r="AY21" s="134"/>
-      <c r="AZ21" s="134"/>
-      <c r="BA21" s="135"/>
-      <c r="BB21" s="151"/>
-      <c r="BC21" s="152"/>
-      <c r="BD21" s="152"/>
-      <c r="BE21" s="152"/>
-      <c r="BF21" s="152"/>
-      <c r="BG21" s="152"/>
-      <c r="BH21" s="152"/>
-      <c r="BI21" s="152"/>
-      <c r="BJ21" s="152"/>
-      <c r="BK21" s="153"/>
-      <c r="BL21" s="33"/>
-      <c r="BM21" s="34"/>
-      <c r="BN21" s="33"/>
-      <c r="BO21" s="33"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="120"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="122"/>
+      <c r="M21" s="165"/>
+      <c r="N21" s="166"/>
+      <c r="O21" s="166"/>
+      <c r="P21" s="166"/>
+      <c r="Q21" s="166"/>
+      <c r="R21" s="166"/>
+      <c r="S21" s="166"/>
+      <c r="T21" s="166"/>
+      <c r="U21" s="166"/>
+      <c r="V21" s="166"/>
+      <c r="W21" s="166"/>
+      <c r="X21" s="166"/>
+      <c r="Y21" s="166"/>
+      <c r="Z21" s="166"/>
+      <c r="AA21" s="166"/>
+      <c r="AB21" s="166"/>
+      <c r="AC21" s="167"/>
+      <c r="AD21" s="131"/>
+      <c r="AE21" s="132"/>
+      <c r="AF21" s="132"/>
+      <c r="AG21" s="133"/>
+      <c r="AH21" s="134"/>
+      <c r="AI21" s="135"/>
+      <c r="AJ21" s="135"/>
+      <c r="AK21" s="136"/>
+      <c r="AL21" s="137"/>
+      <c r="AM21" s="138"/>
+      <c r="AN21" s="138"/>
+      <c r="AO21" s="139"/>
+      <c r="AP21" s="131"/>
+      <c r="AQ21" s="132"/>
+      <c r="AR21" s="132"/>
+      <c r="AS21" s="133"/>
+      <c r="AT21" s="134"/>
+      <c r="AU21" s="135"/>
+      <c r="AV21" s="135"/>
+      <c r="AW21" s="136"/>
+      <c r="AX21" s="137"/>
+      <c r="AY21" s="138"/>
+      <c r="AZ21" s="138"/>
+      <c r="BA21" s="139"/>
+      <c r="BB21" s="155"/>
+      <c r="BC21" s="156"/>
+      <c r="BD21" s="156"/>
+      <c r="BE21" s="156"/>
+      <c r="BF21" s="156"/>
+      <c r="BG21" s="156"/>
+      <c r="BH21" s="156"/>
+      <c r="BI21" s="156"/>
+      <c r="BJ21" s="156"/>
+      <c r="BK21" s="157"/>
+      <c r="BL21" s="29"/>
+      <c r="BM21" s="30"/>
+      <c r="BN21" s="29"/>
+      <c r="BO21" s="29"/>
     </row>
     <row r="22" spans="1:68" ht="13.2">
-      <c r="A22" s="29" t="str">
+      <c r="A22" s="25" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="B22" s="30" t="str">
+      <c r="B22" s="26" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="C22" s="31" t="str">
+      <c r="C22" s="27" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="D22" s="31" t="str">
+      <c r="D22" s="27" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="E22" s="31" t="str">
+      <c r="E22" s="27" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="F22" s="31" t="str">
+      <c r="F22" s="27" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G22" s="31" t="str">
+      <c r="G22" s="27" t="str">
         <f>IF(I22&lt;&gt;"",#REF!,"")</f>
         <v/>
       </c>
-      <c r="H22" s="77" t="str">
+      <c r="H22" s="72" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I22" s="115"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="154"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="155"/>
-      <c r="N22" s="156"/>
-      <c r="O22" s="156"/>
-      <c r="P22" s="156"/>
-      <c r="Q22" s="156"/>
-      <c r="R22" s="156"/>
-      <c r="S22" s="156"/>
-      <c r="T22" s="156"/>
-      <c r="U22" s="156"/>
-      <c r="V22" s="156"/>
-      <c r="W22" s="156"/>
-      <c r="X22" s="156"/>
-      <c r="Y22" s="156"/>
-      <c r="Z22" s="156"/>
-      <c r="AA22" s="156"/>
-      <c r="AB22" s="156"/>
-      <c r="AC22" s="157"/>
-      <c r="AD22" s="122"/>
-      <c r="AE22" s="123"/>
-      <c r="AF22" s="123"/>
-      <c r="AG22" s="123"/>
-      <c r="AH22" s="124"/>
-      <c r="AI22" s="124"/>
-      <c r="AJ22" s="124"/>
-      <c r="AK22" s="124"/>
-      <c r="AL22" s="125"/>
-      <c r="AM22" s="125"/>
-      <c r="AN22" s="125"/>
-      <c r="AO22" s="126"/>
-      <c r="AP22" s="122"/>
-      <c r="AQ22" s="123"/>
-      <c r="AR22" s="123"/>
-      <c r="AS22" s="123"/>
-      <c r="AT22" s="124"/>
-      <c r="AU22" s="124"/>
-      <c r="AV22" s="124"/>
-      <c r="AW22" s="124"/>
-      <c r="AX22" s="125"/>
-      <c r="AY22" s="125"/>
-      <c r="AZ22" s="125"/>
-      <c r="BA22" s="126"/>
-      <c r="BB22" s="158"/>
-      <c r="BC22" s="159"/>
-      <c r="BD22" s="159"/>
-      <c r="BE22" s="159"/>
-      <c r="BF22" s="159"/>
-      <c r="BG22" s="159"/>
-      <c r="BH22" s="159"/>
-      <c r="BI22" s="159"/>
-      <c r="BJ22" s="159"/>
-      <c r="BK22" s="160"/>
-      <c r="BL22" s="33"/>
-      <c r="BM22" s="34"/>
-      <c r="BN22" s="33"/>
-      <c r="BO22" s="33"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="158"/>
+      <c r="L22" s="122"/>
+      <c r="M22" s="159"/>
+      <c r="N22" s="160"/>
+      <c r="O22" s="160"/>
+      <c r="P22" s="160"/>
+      <c r="Q22" s="160"/>
+      <c r="R22" s="160"/>
+      <c r="S22" s="160"/>
+      <c r="T22" s="160"/>
+      <c r="U22" s="160"/>
+      <c r="V22" s="160"/>
+      <c r="W22" s="160"/>
+      <c r="X22" s="160"/>
+      <c r="Y22" s="160"/>
+      <c r="Z22" s="160"/>
+      <c r="AA22" s="160"/>
+      <c r="AB22" s="160"/>
+      <c r="AC22" s="161"/>
+      <c r="AD22" s="126"/>
+      <c r="AE22" s="127"/>
+      <c r="AF22" s="127"/>
+      <c r="AG22" s="127"/>
+      <c r="AH22" s="128"/>
+      <c r="AI22" s="128"/>
+      <c r="AJ22" s="128"/>
+      <c r="AK22" s="128"/>
+      <c r="AL22" s="129"/>
+      <c r="AM22" s="129"/>
+      <c r="AN22" s="129"/>
+      <c r="AO22" s="130"/>
+      <c r="AP22" s="126"/>
+      <c r="AQ22" s="127"/>
+      <c r="AR22" s="127"/>
+      <c r="AS22" s="127"/>
+      <c r="AT22" s="128"/>
+      <c r="AU22" s="128"/>
+      <c r="AV22" s="128"/>
+      <c r="AW22" s="128"/>
+      <c r="AX22" s="129"/>
+      <c r="AY22" s="129"/>
+      <c r="AZ22" s="129"/>
+      <c r="BA22" s="130"/>
+      <c r="BB22" s="162"/>
+      <c r="BC22" s="163"/>
+      <c r="BD22" s="163"/>
+      <c r="BE22" s="163"/>
+      <c r="BF22" s="163"/>
+      <c r="BG22" s="163"/>
+      <c r="BH22" s="163"/>
+      <c r="BI22" s="163"/>
+      <c r="BJ22" s="163"/>
+      <c r="BK22" s="164"/>
+      <c r="BL22" s="29"/>
+      <c r="BM22" s="30"/>
+      <c r="BN22" s="29"/>
+      <c r="BO22" s="29"/>
     </row>
     <row r="23" spans="1:68" ht="13.2">
-      <c r="A23" s="29" t="str">
+      <c r="A23" s="25" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="B23" s="30" t="str">
+      <c r="B23" s="26" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="C23" s="31" t="str">
+      <c r="C23" s="27" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="D23" s="31" t="str">
+      <c r="D23" s="27" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="E23" s="31" t="str">
+      <c r="E23" s="27" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="F23" s="31" t="str">
+      <c r="F23" s="27" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="77" t="str">
+      <c r="G23" s="27"/>
+      <c r="H23" s="72" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I23" s="115"/>
-      <c r="J23" s="116"/>
-      <c r="K23" s="154"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="155"/>
-      <c r="N23" s="156"/>
-      <c r="O23" s="156"/>
-      <c r="P23" s="156"/>
-      <c r="Q23" s="156"/>
-      <c r="R23" s="156"/>
-      <c r="S23" s="156"/>
-      <c r="T23" s="156"/>
-      <c r="U23" s="156"/>
-      <c r="V23" s="156"/>
-      <c r="W23" s="156"/>
-      <c r="X23" s="156"/>
-      <c r="Y23" s="156"/>
-      <c r="Z23" s="156"/>
-      <c r="AA23" s="156"/>
-      <c r="AB23" s="156"/>
-      <c r="AC23" s="157"/>
-      <c r="AD23" s="122"/>
-      <c r="AE23" s="123"/>
-      <c r="AF23" s="123"/>
-      <c r="AG23" s="123"/>
-      <c r="AH23" s="124"/>
-      <c r="AI23" s="124"/>
-      <c r="AJ23" s="124"/>
-      <c r="AK23" s="124"/>
-      <c r="AL23" s="125"/>
-      <c r="AM23" s="125"/>
-      <c r="AN23" s="125"/>
-      <c r="AO23" s="126"/>
-      <c r="AP23" s="122"/>
-      <c r="AQ23" s="123"/>
-      <c r="AR23" s="123"/>
-      <c r="AS23" s="123"/>
-      <c r="AT23" s="124"/>
-      <c r="AU23" s="124"/>
-      <c r="AV23" s="124"/>
-      <c r="AW23" s="124"/>
-      <c r="AX23" s="125"/>
-      <c r="AY23" s="125"/>
-      <c r="AZ23" s="125"/>
-      <c r="BA23" s="126"/>
-      <c r="BB23" s="158"/>
-      <c r="BC23" s="159"/>
-      <c r="BD23" s="159"/>
-      <c r="BE23" s="159"/>
-      <c r="BF23" s="159"/>
-      <c r="BG23" s="159"/>
-      <c r="BH23" s="159"/>
-      <c r="BI23" s="159"/>
-      <c r="BJ23" s="159"/>
-      <c r="BK23" s="160"/>
-      <c r="BL23" s="33"/>
-      <c r="BM23" s="34"/>
-      <c r="BN23" s="33"/>
-      <c r="BO23" s="33"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="120"/>
+      <c r="K23" s="158"/>
+      <c r="L23" s="122"/>
+      <c r="M23" s="159"/>
+      <c r="N23" s="160"/>
+      <c r="O23" s="160"/>
+      <c r="P23" s="160"/>
+      <c r="Q23" s="160"/>
+      <c r="R23" s="160"/>
+      <c r="S23" s="160"/>
+      <c r="T23" s="160"/>
+      <c r="U23" s="160"/>
+      <c r="V23" s="160"/>
+      <c r="W23" s="160"/>
+      <c r="X23" s="160"/>
+      <c r="Y23" s="160"/>
+      <c r="Z23" s="160"/>
+      <c r="AA23" s="160"/>
+      <c r="AB23" s="160"/>
+      <c r="AC23" s="161"/>
+      <c r="AD23" s="126"/>
+      <c r="AE23" s="127"/>
+      <c r="AF23" s="127"/>
+      <c r="AG23" s="127"/>
+      <c r="AH23" s="128"/>
+      <c r="AI23" s="128"/>
+      <c r="AJ23" s="128"/>
+      <c r="AK23" s="128"/>
+      <c r="AL23" s="129"/>
+      <c r="AM23" s="129"/>
+      <c r="AN23" s="129"/>
+      <c r="AO23" s="130"/>
+      <c r="AP23" s="126"/>
+      <c r="AQ23" s="127"/>
+      <c r="AR23" s="127"/>
+      <c r="AS23" s="127"/>
+      <c r="AT23" s="128"/>
+      <c r="AU23" s="128"/>
+      <c r="AV23" s="128"/>
+      <c r="AW23" s="128"/>
+      <c r="AX23" s="129"/>
+      <c r="AY23" s="129"/>
+      <c r="AZ23" s="129"/>
+      <c r="BA23" s="130"/>
+      <c r="BB23" s="162"/>
+      <c r="BC23" s="163"/>
+      <c r="BD23" s="163"/>
+      <c r="BE23" s="163"/>
+      <c r="BF23" s="163"/>
+      <c r="BG23" s="163"/>
+      <c r="BH23" s="163"/>
+      <c r="BI23" s="163"/>
+      <c r="BJ23" s="163"/>
+      <c r="BK23" s="164"/>
+      <c r="BL23" s="29"/>
+      <c r="BM23" s="30"/>
+      <c r="BN23" s="29"/>
+      <c r="BO23" s="29"/>
     </row>
     <row r="24" spans="1:68" ht="13.8" thickBot="1">
-      <c r="A24" s="29" t="str">
+      <c r="A24" s="25" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B24" s="30" t="str">
+      <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C24" s="31" t="str">
+      <c r="C24" s="27" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="D24" s="31" t="str">
+      <c r="D24" s="27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="E24" s="31" t="str">
+      <c r="E24" s="27" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="F24" s="31" t="str">
+      <c r="F24" s="27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G24" s="31" t="str">
+      <c r="G24" s="27" t="str">
         <f t="shared" ref="G24" si="14">IF(I24&lt;&gt;"",M24,"")</f>
         <v/>
       </c>
-      <c r="H24" s="77" t="str">
+      <c r="H24" s="72" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="I24" s="183"/>
-      <c r="J24" s="184"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="186"/>
-      <c r="M24" s="187"/>
-      <c r="N24" s="188"/>
-      <c r="O24" s="188"/>
-      <c r="P24" s="188"/>
-      <c r="Q24" s="188"/>
-      <c r="R24" s="188"/>
-      <c r="S24" s="188"/>
-      <c r="T24" s="188"/>
-      <c r="U24" s="188"/>
-      <c r="V24" s="188"/>
-      <c r="W24" s="188"/>
-      <c r="X24" s="188"/>
-      <c r="Y24" s="188"/>
-      <c r="Z24" s="188"/>
-      <c r="AA24" s="188"/>
-      <c r="AB24" s="188"/>
-      <c r="AC24" s="189"/>
-      <c r="AD24" s="190"/>
-      <c r="AE24" s="191"/>
-      <c r="AF24" s="191"/>
-      <c r="AG24" s="191"/>
-      <c r="AH24" s="164"/>
-      <c r="AI24" s="164"/>
-      <c r="AJ24" s="164"/>
-      <c r="AK24" s="164"/>
-      <c r="AL24" s="240"/>
-      <c r="AM24" s="241"/>
-      <c r="AN24" s="241"/>
-      <c r="AO24" s="242"/>
-      <c r="AP24" s="190"/>
-      <c r="AQ24" s="191"/>
-      <c r="AR24" s="191"/>
-      <c r="AS24" s="191"/>
-      <c r="AT24" s="164"/>
-      <c r="AU24" s="164"/>
-      <c r="AV24" s="164"/>
-      <c r="AW24" s="164"/>
-      <c r="AX24" s="165"/>
-      <c r="AY24" s="165"/>
-      <c r="AZ24" s="165"/>
-      <c r="BA24" s="166"/>
-      <c r="BB24" s="167"/>
-      <c r="BC24" s="168"/>
-      <c r="BD24" s="168"/>
-      <c r="BE24" s="168"/>
-      <c r="BF24" s="168"/>
-      <c r="BG24" s="168"/>
-      <c r="BH24" s="168"/>
-      <c r="BI24" s="168"/>
-      <c r="BJ24" s="168"/>
-      <c r="BK24" s="169"/>
-      <c r="BL24" s="33"/>
-      <c r="BM24" s="34"/>
-      <c r="BN24" s="33"/>
-      <c r="BO24" s="33"/>
+      <c r="I24" s="187"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="189"/>
+      <c r="L24" s="190"/>
+      <c r="M24" s="191"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="192"/>
+      <c r="Q24" s="192"/>
+      <c r="R24" s="192"/>
+      <c r="S24" s="192"/>
+      <c r="T24" s="192"/>
+      <c r="U24" s="192"/>
+      <c r="V24" s="192"/>
+      <c r="W24" s="192"/>
+      <c r="X24" s="192"/>
+      <c r="Y24" s="192"/>
+      <c r="Z24" s="192"/>
+      <c r="AA24" s="192"/>
+      <c r="AB24" s="192"/>
+      <c r="AC24" s="193"/>
+      <c r="AD24" s="194"/>
+      <c r="AE24" s="195"/>
+      <c r="AF24" s="195"/>
+      <c r="AG24" s="195"/>
+      <c r="AH24" s="168"/>
+      <c r="AI24" s="168"/>
+      <c r="AJ24" s="168"/>
+      <c r="AK24" s="168"/>
+      <c r="AL24" s="241"/>
+      <c r="AM24" s="242"/>
+      <c r="AN24" s="242"/>
+      <c r="AO24" s="243"/>
+      <c r="AP24" s="194"/>
+      <c r="AQ24" s="195"/>
+      <c r="AR24" s="195"/>
+      <c r="AS24" s="195"/>
+      <c r="AT24" s="168"/>
+      <c r="AU24" s="168"/>
+      <c r="AV24" s="168"/>
+      <c r="AW24" s="168"/>
+      <c r="AX24" s="169"/>
+      <c r="AY24" s="169"/>
+      <c r="AZ24" s="169"/>
+      <c r="BA24" s="170"/>
+      <c r="BB24" s="171"/>
+      <c r="BC24" s="172"/>
+      <c r="BD24" s="172"/>
+      <c r="BE24" s="172"/>
+      <c r="BF24" s="172"/>
+      <c r="BG24" s="172"/>
+      <c r="BH24" s="172"/>
+      <c r="BI24" s="172"/>
+      <c r="BJ24" s="172"/>
+      <c r="BK24" s="173"/>
+      <c r="BL24" s="29"/>
+      <c r="BM24" s="30"/>
+      <c r="BN24" s="29"/>
+      <c r="BO24" s="29"/>
     </row>
     <row r="25" spans="1:68" ht="1.5" customHeight="1">
-      <c r="A25" s="29"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="28"/>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="38"/>
-      <c r="AE25" s="38"/>
-      <c r="AF25" s="38"/>
-      <c r="AG25" s="38"/>
-      <c r="AH25" s="39"/>
-      <c r="AI25" s="39"/>
-      <c r="AJ25" s="39"/>
-      <c r="AK25" s="39"/>
-      <c r="AL25" s="40"/>
-      <c r="AM25" s="40"/>
-      <c r="AN25" s="40"/>
-      <c r="AO25" s="40"/>
-      <c r="AP25" s="38"/>
-      <c r="AQ25" s="38"/>
-      <c r="AR25" s="38"/>
-      <c r="AS25" s="38"/>
-      <c r="AT25" s="39"/>
-      <c r="AU25" s="39"/>
-      <c r="AV25" s="39"/>
-      <c r="AW25" s="39"/>
-      <c r="AX25" s="40"/>
-      <c r="AY25" s="40"/>
-      <c r="AZ25" s="40"/>
-      <c r="BA25" s="40"/>
-      <c r="BB25" s="41"/>
-      <c r="BC25" s="41"/>
-      <c r="BD25" s="41"/>
-      <c r="BE25" s="41"/>
-      <c r="BF25" s="41"/>
-      <c r="BG25" s="41"/>
-      <c r="BH25" s="41"/>
-      <c r="BI25" s="41"/>
-      <c r="BJ25" s="41"/>
-      <c r="BK25" s="42"/>
-      <c r="BL25" s="33"/>
-      <c r="BM25" s="34"/>
-      <c r="BN25" s="33"/>
-      <c r="BO25" s="33"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="34"/>
+      <c r="AI25" s="34"/>
+      <c r="AJ25" s="34"/>
+      <c r="AK25" s="34"/>
+      <c r="AL25" s="35"/>
+      <c r="AM25" s="35"/>
+      <c r="AN25" s="35"/>
+      <c r="AO25" s="35"/>
+      <c r="AP25" s="33"/>
+      <c r="AQ25" s="33"/>
+      <c r="AR25" s="33"/>
+      <c r="AS25" s="33"/>
+      <c r="AT25" s="34"/>
+      <c r="AU25" s="34"/>
+      <c r="AV25" s="34"/>
+      <c r="AW25" s="34"/>
+      <c r="AX25" s="35"/>
+      <c r="AY25" s="35"/>
+      <c r="AZ25" s="35"/>
+      <c r="BA25" s="35"/>
+      <c r="BB25" s="36"/>
+      <c r="BC25" s="36"/>
+      <c r="BD25" s="36"/>
+      <c r="BE25" s="36"/>
+      <c r="BF25" s="36"/>
+      <c r="BG25" s="36"/>
+      <c r="BH25" s="36"/>
+      <c r="BI25" s="36"/>
+      <c r="BJ25" s="36"/>
+      <c r="BK25" s="37"/>
+      <c r="BL25" s="29"/>
+      <c r="BM25" s="30"/>
+      <c r="BN25" s="29"/>
+      <c r="BO25" s="29"/>
     </row>
     <row r="26" spans="1:68" ht="13.5" customHeight="1">
-      <c r="A26" s="11"/>
+      <c r="A26" s="9"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="43" t="s">
+      <c r="I26" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="M26" s="27" t="s">
+      <c r="J26" s="39"/>
+      <c r="K26" s="39"/>
+      <c r="M26" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="N26" s="45"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="27" t="s">
+      <c r="N26" s="40"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="39"/>
+      <c r="Q26" s="39"/>
+      <c r="S26" s="39"/>
+      <c r="T26" s="39"/>
+      <c r="U26" s="39"/>
+      <c r="V26" s="39"/>
+      <c r="W26" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
-      <c r="Z26" s="44"/>
-      <c r="AA26" s="44"/>
-      <c r="AD26" s="44"/>
-      <c r="AE26" s="44"/>
-      <c r="AF26" s="27" t="s">
+      <c r="X26" s="39"/>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="39"/>
+      <c r="AA26" s="39"/>
+      <c r="AD26" s="39"/>
+      <c r="AE26" s="39"/>
+      <c r="AF26" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="AG26" s="44"/>
-      <c r="AH26" s="44"/>
-      <c r="AI26" s="44"/>
-      <c r="AJ26" s="44"/>
-      <c r="AK26" s="44"/>
-      <c r="AL26" s="44"/>
-      <c r="AO26" s="195" t="s">
+      <c r="AG26" s="39"/>
+      <c r="AH26" s="39"/>
+      <c r="AI26" s="39"/>
+      <c r="AJ26" s="39"/>
+      <c r="AK26" s="39"/>
+      <c r="AL26" s="39"/>
+      <c r="AO26" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="AP26" s="196"/>
-      <c r="AQ26" s="196"/>
-      <c r="AR26" s="196"/>
-      <c r="AS26" s="196"/>
-      <c r="AT26" s="196"/>
-      <c r="AU26" s="196"/>
-      <c r="AV26" s="196"/>
-      <c r="AW26" s="196"/>
-      <c r="AX26" s="196"/>
-      <c r="AY26" s="196"/>
-      <c r="AZ26" s="196"/>
-      <c r="BA26" s="196"/>
-      <c r="BB26" s="196"/>
-      <c r="BC26" s="196"/>
-      <c r="BD26" s="196"/>
-      <c r="BE26" s="196"/>
-      <c r="BF26" s="196"/>
-      <c r="BG26" s="196"/>
-      <c r="BH26" s="196"/>
-      <c r="BI26" s="196"/>
-      <c r="BJ26" s="196"/>
-      <c r="BK26" s="197"/>
+      <c r="AP26" s="200"/>
+      <c r="AQ26" s="200"/>
+      <c r="AR26" s="200"/>
+      <c r="AS26" s="200"/>
+      <c r="AT26" s="200"/>
+      <c r="AU26" s="200"/>
+      <c r="AV26" s="200"/>
+      <c r="AW26" s="200"/>
+      <c r="AX26" s="200"/>
+      <c r="AY26" s="200"/>
+      <c r="AZ26" s="200"/>
+      <c r="BA26" s="200"/>
+      <c r="BB26" s="200"/>
+      <c r="BC26" s="200"/>
+      <c r="BD26" s="200"/>
+      <c r="BE26" s="200"/>
+      <c r="BF26" s="200"/>
+      <c r="BG26" s="200"/>
+      <c r="BH26" s="200"/>
+      <c r="BI26" s="200"/>
+      <c r="BJ26" s="200"/>
+      <c r="BK26" s="201"/>
     </row>
     <row r="27" spans="1:68" ht="21.75" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="27" t="s">
+      <c r="A27" s="9"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="177"/>
-      <c r="T27" s="177"/>
-      <c r="U27" s="177"/>
-      <c r="V27" s="177"/>
-      <c r="W27" s="177"/>
-      <c r="X27" s="177"/>
-      <c r="Y27" s="177"/>
-      <c r="Z27" s="177"/>
-      <c r="AA27" s="177"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="177"/>
-      <c r="AE27" s="177"/>
-      <c r="AF27" s="177"/>
-      <c r="AG27" s="177"/>
-      <c r="AH27" s="177"/>
-      <c r="AI27" s="177"/>
-      <c r="AJ27" s="177"/>
-      <c r="AK27" s="177"/>
-      <c r="AL27" s="177"/>
-      <c r="AM27" s="48"/>
-      <c r="AN27" s="44"/>
-      <c r="AO27" s="198"/>
-      <c r="AP27" s="199"/>
-      <c r="AQ27" s="199"/>
-      <c r="AR27" s="199"/>
-      <c r="AS27" s="199"/>
-      <c r="AT27" s="199"/>
-      <c r="AU27" s="199"/>
-      <c r="AV27" s="199"/>
-      <c r="AW27" s="199"/>
-      <c r="AX27" s="199"/>
-      <c r="AY27" s="199"/>
-      <c r="AZ27" s="199"/>
-      <c r="BA27" s="199"/>
-      <c r="BB27" s="199"/>
-      <c r="BC27" s="199"/>
-      <c r="BD27" s="199"/>
-      <c r="BE27" s="199"/>
-      <c r="BF27" s="199"/>
-      <c r="BG27" s="199"/>
-      <c r="BH27" s="199"/>
-      <c r="BI27" s="199"/>
-      <c r="BJ27" s="199"/>
-      <c r="BK27" s="200"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="181"/>
+      <c r="T27" s="181"/>
+      <c r="U27" s="181"/>
+      <c r="V27" s="181"/>
+      <c r="W27" s="181"/>
+      <c r="X27" s="181"/>
+      <c r="Y27" s="181"/>
+      <c r="Z27" s="181"/>
+      <c r="AA27" s="181"/>
+      <c r="AB27" s="43"/>
+      <c r="AC27" s="43"/>
+      <c r="AD27" s="181"/>
+      <c r="AE27" s="181"/>
+      <c r="AF27" s="181"/>
+      <c r="AG27" s="181"/>
+      <c r="AH27" s="181"/>
+      <c r="AI27" s="181"/>
+      <c r="AJ27" s="181"/>
+      <c r="AK27" s="181"/>
+      <c r="AL27" s="181"/>
+      <c r="AM27" s="43"/>
+      <c r="AN27" s="39"/>
+      <c r="AO27" s="202"/>
+      <c r="AP27" s="203"/>
+      <c r="AQ27" s="203"/>
+      <c r="AR27" s="203"/>
+      <c r="AS27" s="203"/>
+      <c r="AT27" s="203"/>
+      <c r="AU27" s="203"/>
+      <c r="AV27" s="203"/>
+      <c r="AW27" s="203"/>
+      <c r="AX27" s="203"/>
+      <c r="AY27" s="203"/>
+      <c r="AZ27" s="203"/>
+      <c r="BA27" s="203"/>
+      <c r="BB27" s="203"/>
+      <c r="BC27" s="203"/>
+      <c r="BD27" s="203"/>
+      <c r="BE27" s="203"/>
+      <c r="BF27" s="203"/>
+      <c r="BG27" s="203"/>
+      <c r="BH27" s="203"/>
+      <c r="BI27" s="203"/>
+      <c r="BJ27" s="203"/>
+      <c r="BK27" s="204"/>
     </row>
     <row r="28" spans="1:68" ht="3" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="44"/>
-      <c r="AC28" s="44"/>
-      <c r="AD28" s="50"/>
-      <c r="AE28" s="50"/>
-      <c r="AF28" s="50"/>
-      <c r="AG28" s="50"/>
-      <c r="AH28" s="50"/>
-      <c r="AI28" s="50"/>
-      <c r="AJ28" s="50"/>
-      <c r="AK28" s="50"/>
-      <c r="AL28" s="50"/>
-      <c r="AM28" s="44"/>
-      <c r="AN28" s="44"/>
-      <c r="AO28" s="51"/>
-      <c r="AP28" s="50"/>
-      <c r="AQ28" s="50"/>
-      <c r="AR28" s="50"/>
-      <c r="AS28" s="50"/>
-      <c r="AT28" s="50"/>
-      <c r="AU28" s="50"/>
-      <c r="AV28" s="50"/>
-      <c r="AW28" s="50"/>
-      <c r="AX28" s="50"/>
-      <c r="AY28" s="50"/>
-      <c r="AZ28" s="50"/>
-      <c r="BA28" s="50"/>
-      <c r="BB28" s="50"/>
-      <c r="BC28" s="50"/>
-      <c r="BD28" s="50"/>
-      <c r="BE28" s="50"/>
-      <c r="BF28" s="50"/>
-      <c r="BG28" s="50"/>
-      <c r="BH28" s="50"/>
-      <c r="BI28" s="50"/>
-      <c r="BJ28" s="50"/>
-      <c r="BK28" s="52"/>
+      <c r="A28" s="9"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="39"/>
+      <c r="S28" s="45"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="45"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="45"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="45"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="45"/>
+      <c r="AB28" s="39"/>
+      <c r="AC28" s="39"/>
+      <c r="AD28" s="45"/>
+      <c r="AE28" s="45"/>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="45"/>
+      <c r="AH28" s="45"/>
+      <c r="AI28" s="45"/>
+      <c r="AJ28" s="45"/>
+      <c r="AK28" s="45"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="39"/>
+      <c r="AN28" s="39"/>
+      <c r="AO28" s="46"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+      <c r="AR28" s="45"/>
+      <c r="AS28" s="45"/>
+      <c r="AT28" s="45"/>
+      <c r="AU28" s="45"/>
+      <c r="AV28" s="45"/>
+      <c r="AW28" s="45"/>
+      <c r="AX28" s="45"/>
+      <c r="AY28" s="45"/>
+      <c r="AZ28" s="45"/>
+      <c r="BA28" s="45"/>
+      <c r="BB28" s="45"/>
+      <c r="BC28" s="45"/>
+      <c r="BD28" s="45"/>
+      <c r="BE28" s="45"/>
+      <c r="BF28" s="45"/>
+      <c r="BG28" s="45"/>
+      <c r="BH28" s="45"/>
+      <c r="BI28" s="45"/>
+      <c r="BJ28" s="45"/>
+      <c r="BK28" s="47"/>
     </row>
     <row r="29" spans="1:68" ht="10.5" customHeight="1">
-      <c r="A29" s="11"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="178"/>
-      <c r="N29" s="178"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="179"/>
-      <c r="W29" s="179"/>
-      <c r="X29" s="54"/>
-      <c r="Y29" s="53"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="54"/>
-      <c r="AC29" s="54"/>
-      <c r="AD29" s="53"/>
-      <c r="AE29" s="55"/>
-      <c r="AF29" s="54"/>
-      <c r="AG29" s="54"/>
-      <c r="AH29" s="54"/>
-      <c r="AI29" s="54"/>
-      <c r="AJ29" s="54"/>
-      <c r="AK29" s="54"/>
-      <c r="AL29" s="54"/>
-      <c r="AM29" s="48"/>
-      <c r="AN29" s="44"/>
-      <c r="AO29" s="180" t="s">
+      <c r="A29" s="9"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="183"/>
+      <c r="W29" s="183"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="48"/>
+      <c r="AE29" s="50"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="49"/>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
+      <c r="AL29" s="49"/>
+      <c r="AM29" s="43"/>
+      <c r="AN29" s="39"/>
+      <c r="AO29" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="AP29" s="181"/>
-      <c r="AQ29" s="181"/>
-      <c r="AR29" s="181"/>
-      <c r="AS29" s="181"/>
-      <c r="AT29" s="181"/>
-      <c r="AU29" s="181"/>
-      <c r="AV29" s="181"/>
-      <c r="AW29" s="181"/>
-      <c r="AX29" s="181"/>
-      <c r="AY29" s="181"/>
-      <c r="AZ29" s="181"/>
-      <c r="BA29" s="45"/>
-      <c r="BB29" s="45"/>
-      <c r="BC29" s="57"/>
-      <c r="BD29" s="57"/>
-      <c r="BE29" s="57"/>
-      <c r="BF29" s="57"/>
-      <c r="BG29" s="57"/>
-      <c r="BH29" s="57"/>
-      <c r="BI29" s="57"/>
-      <c r="BJ29" s="57"/>
-      <c r="BK29" s="58"/>
+      <c r="AP29" s="185"/>
+      <c r="AQ29" s="185"/>
+      <c r="AR29" s="185"/>
+      <c r="AS29" s="185"/>
+      <c r="AT29" s="185"/>
+      <c r="AU29" s="185"/>
+      <c r="AV29" s="185"/>
+      <c r="AW29" s="185"/>
+      <c r="AX29" s="185"/>
+      <c r="AY29" s="185"/>
+      <c r="AZ29" s="185"/>
+      <c r="BA29" s="40"/>
+      <c r="BB29" s="40"/>
+      <c r="BC29" s="52"/>
+      <c r="BD29" s="52"/>
+      <c r="BE29" s="52"/>
+      <c r="BF29" s="52"/>
+      <c r="BG29" s="52"/>
+      <c r="BH29" s="52"/>
+      <c r="BI29" s="52"/>
+      <c r="BJ29" s="52"/>
+      <c r="BK29" s="53"/>
       <c r="BP29" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:68" ht="2.1" customHeight="1">
-      <c r="A30" s="11"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="59"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="60"/>
+      <c r="A30" s="9"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="54"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="55"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="45"/>
-      <c r="X30" s="45"/>
-      <c r="AO30" s="61"/>
-      <c r="BA30" s="59"/>
-      <c r="BB30" s="59"/>
-      <c r="BK30" s="25"/>
+      <c r="V30" s="40"/>
+      <c r="W30" s="40"/>
+      <c r="X30" s="40"/>
+      <c r="AO30" s="56"/>
+      <c r="BA30" s="54"/>
+      <c r="BB30" s="54"/>
+      <c r="BK30" s="21"/>
     </row>
     <row r="31" spans="1:68" ht="10.5" customHeight="1">
-      <c r="A31" s="62"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="54"/>
-      <c r="M31" s="54"/>
-      <c r="N31" s="65"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="55"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="55"/>
-      <c r="V31" s="65"/>
-      <c r="W31" s="65"/>
-      <c r="X31" s="65"/>
-      <c r="Y31" s="54"/>
-      <c r="Z31" s="54"/>
-      <c r="AA31" s="54"/>
-      <c r="AB31" s="54"/>
-      <c r="AC31" s="54"/>
-      <c r="AD31" s="54"/>
-      <c r="AE31" s="54"/>
-      <c r="AF31" s="54"/>
-      <c r="AG31" s="54"/>
-      <c r="AH31" s="54"/>
-      <c r="AI31" s="54"/>
-      <c r="AJ31" s="54"/>
-      <c r="AK31" s="54"/>
-      <c r="AL31" s="54"/>
-      <c r="AM31" s="54"/>
-      <c r="AN31" s="66"/>
-      <c r="AO31" s="61"/>
-      <c r="AP31" s="80"/>
-      <c r="AR31" s="182" t="s">
+      <c r="A31" s="57"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="59"/>
+      <c r="K31" s="49"/>
+      <c r="L31" s="49"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="60"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="60"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="49"/>
+      <c r="AA31" s="49"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="49"/>
+      <c r="AE31" s="49"/>
+      <c r="AF31" s="49"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
+      <c r="AL31" s="49"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="61"/>
+      <c r="AO31" s="56"/>
+      <c r="AP31" s="75"/>
+      <c r="AR31" s="186" t="s">
         <v>36</v>
       </c>
-      <c r="AS31" s="182"/>
-      <c r="AT31" s="182"/>
-      <c r="AU31" s="182"/>
-      <c r="AV31" s="182"/>
-      <c r="AW31" s="182"/>
-      <c r="AX31" s="182"/>
-      <c r="AY31" s="182"/>
-      <c r="AZ31" s="182"/>
-      <c r="BA31" s="176" t="s">
+      <c r="AS31" s="186"/>
+      <c r="AT31" s="186"/>
+      <c r="AU31" s="186"/>
+      <c r="AV31" s="186"/>
+      <c r="AW31" s="186"/>
+      <c r="AX31" s="186"/>
+      <c r="AY31" s="186"/>
+      <c r="AZ31" s="186"/>
+      <c r="BA31" s="180" t="s">
         <v>37</v>
       </c>
-      <c r="BB31" s="176"/>
-      <c r="BC31" s="176"/>
-      <c r="BD31" s="176"/>
-      <c r="BE31" s="176"/>
-      <c r="BF31" s="176"/>
-      <c r="BG31" s="176"/>
-      <c r="BH31" s="176"/>
-      <c r="BI31" s="176"/>
-      <c r="BJ31" s="176"/>
-      <c r="BK31" s="25"/>
+      <c r="BB31" s="180"/>
+      <c r="BC31" s="180"/>
+      <c r="BD31" s="180"/>
+      <c r="BE31" s="180"/>
+      <c r="BF31" s="180"/>
+      <c r="BG31" s="180"/>
+      <c r="BH31" s="180"/>
+      <c r="BI31" s="180"/>
+      <c r="BJ31" s="180"/>
+      <c r="BK31" s="21"/>
     </row>
     <row r="32" spans="1:68" ht="2.1" customHeight="1">
-      <c r="A32" s="11"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="59"/>
-      <c r="N32" s="45"/>
+      <c r="A32" s="9"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="54"/>
+      <c r="N32" s="40"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
@@ -6069,509 +6099,509 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
-      <c r="V32" s="45"/>
-      <c r="W32" s="45"/>
-      <c r="X32" s="45"/>
-      <c r="AO32" s="61"/>
-      <c r="AR32" s="68"/>
-      <c r="AS32" s="68"/>
-      <c r="AT32" s="68"/>
-      <c r="AU32" s="68"/>
-      <c r="AV32" s="68"/>
-      <c r="AW32" s="68"/>
-      <c r="BD32" s="45"/>
-      <c r="BK32" s="25"/>
+      <c r="V32" s="40"/>
+      <c r="W32" s="40"/>
+      <c r="X32" s="40"/>
+      <c r="AO32" s="56"/>
+      <c r="AR32" s="63"/>
+      <c r="AS32" s="63"/>
+      <c r="AT32" s="63"/>
+      <c r="AU32" s="63"/>
+      <c r="AV32" s="63"/>
+      <c r="AW32" s="63"/>
+      <c r="BD32" s="40"/>
+      <c r="BK32" s="21"/>
     </row>
     <row r="33" spans="1:63" ht="10.5" customHeight="1">
-      <c r="A33" s="11"/>
-      <c r="I33" s="43" t="s">
+      <c r="A33" s="9"/>
+      <c r="I33" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="J33" s="59"/>
+      <c r="J33" s="54"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="45" t="s">
+      <c r="Q33" s="40" t="s">
         <v>39</v>
       </c>
       <c r="R33" s="1"/>
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="45"/>
-      <c r="X33" s="45"/>
-      <c r="AD33" s="45" t="s">
+      <c r="V33" s="40"/>
+      <c r="W33" s="40"/>
+      <c r="X33" s="40"/>
+      <c r="AD33" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="AO33" s="61"/>
-      <c r="AP33" s="79"/>
-      <c r="AR33" s="181" t="s">
+      <c r="AO33" s="56"/>
+      <c r="AP33" s="74"/>
+      <c r="AR33" s="185" t="s">
         <v>41</v>
       </c>
-      <c r="AS33" s="181"/>
-      <c r="AT33" s="181"/>
-      <c r="AU33" s="181"/>
-      <c r="AV33" s="181"/>
-      <c r="AW33" s="181"/>
-      <c r="AY33" s="59"/>
-      <c r="BA33" s="176" t="s">
+      <c r="AS33" s="185"/>
+      <c r="AT33" s="185"/>
+      <c r="AU33" s="185"/>
+      <c r="AV33" s="185"/>
+      <c r="AW33" s="185"/>
+      <c r="AY33" s="54"/>
+      <c r="BA33" s="180" t="s">
         <v>42</v>
       </c>
-      <c r="BB33" s="176"/>
-      <c r="BC33" s="176"/>
-      <c r="BD33" s="176"/>
-      <c r="BE33" s="176"/>
-      <c r="BF33" s="176"/>
-      <c r="BG33" s="176"/>
-      <c r="BH33" s="176"/>
-      <c r="BI33" s="176"/>
-      <c r="BJ33" s="176"/>
-      <c r="BK33" s="25"/>
+      <c r="BB33" s="180"/>
+      <c r="BC33" s="180"/>
+      <c r="BD33" s="180"/>
+      <c r="BE33" s="180"/>
+      <c r="BF33" s="180"/>
+      <c r="BG33" s="180"/>
+      <c r="BH33" s="180"/>
+      <c r="BI33" s="180"/>
+      <c r="BJ33" s="180"/>
+      <c r="BK33" s="21"/>
     </row>
     <row r="34" spans="1:63" ht="2.1" customHeight="1">
-      <c r="A34" s="11"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="59"/>
-      <c r="N34" s="59"/>
-      <c r="V34" s="45"/>
-      <c r="W34" s="45"/>
-      <c r="X34" s="45"/>
-      <c r="AO34" s="61"/>
-      <c r="AR34" s="56"/>
-      <c r="AS34" s="56"/>
-      <c r="AT34" s="56"/>
-      <c r="AU34" s="56"/>
-      <c r="AV34" s="56"/>
-      <c r="AW34" s="56"/>
-      <c r="BC34" s="59"/>
-      <c r="BK34" s="25"/>
+      <c r="A34" s="9"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="54"/>
+      <c r="N34" s="54"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="40"/>
+      <c r="AO34" s="56"/>
+      <c r="AR34" s="51"/>
+      <c r="AS34" s="51"/>
+      <c r="AT34" s="51"/>
+      <c r="AU34" s="51"/>
+      <c r="AV34" s="51"/>
+      <c r="AW34" s="51"/>
+      <c r="BC34" s="54"/>
+      <c r="BK34" s="21"/>
     </row>
     <row r="35" spans="1:63" ht="10.5" customHeight="1">
-      <c r="A35" s="11"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="59"/>
-      <c r="N35" s="59"/>
-      <c r="V35" s="45"/>
-      <c r="W35" s="45"/>
-      <c r="X35" s="45"/>
-      <c r="AD35" s="175"/>
-      <c r="AE35" s="175"/>
-      <c r="AF35" s="175"/>
-      <c r="AG35" s="175"/>
-      <c r="AH35" s="175"/>
-      <c r="AI35" s="175"/>
-      <c r="AJ35" s="175"/>
-      <c r="AK35" s="175"/>
-      <c r="AL35" s="175"/>
-      <c r="AO35" s="61"/>
-      <c r="AP35" s="78"/>
-      <c r="AR35" s="45" t="s">
+      <c r="A35" s="9"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="V35" s="40"/>
+      <c r="W35" s="40"/>
+      <c r="X35" s="40"/>
+      <c r="AD35" s="179"/>
+      <c r="AE35" s="179"/>
+      <c r="AF35" s="179"/>
+      <c r="AG35" s="179"/>
+      <c r="AH35" s="179"/>
+      <c r="AI35" s="179"/>
+      <c r="AJ35" s="179"/>
+      <c r="AK35" s="179"/>
+      <c r="AL35" s="179"/>
+      <c r="AO35" s="56"/>
+      <c r="AP35" s="73"/>
+      <c r="AR35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="AS35" s="45"/>
-      <c r="AT35" s="45"/>
-      <c r="AU35" s="45"/>
-      <c r="AV35" s="45"/>
-      <c r="AW35" s="45"/>
-      <c r="AY35" s="59"/>
-      <c r="BA35" s="176" t="s">
+      <c r="AS35" s="40"/>
+      <c r="AT35" s="40"/>
+      <c r="AU35" s="40"/>
+      <c r="AV35" s="40"/>
+      <c r="AW35" s="40"/>
+      <c r="AY35" s="54"/>
+      <c r="BA35" s="180" t="s">
         <v>44</v>
       </c>
-      <c r="BB35" s="176"/>
-      <c r="BC35" s="176"/>
-      <c r="BD35" s="176"/>
-      <c r="BE35" s="176"/>
-      <c r="BF35" s="176"/>
-      <c r="BG35" s="176"/>
-      <c r="BH35" s="176"/>
-      <c r="BI35" s="176"/>
-      <c r="BJ35" s="176"/>
-      <c r="BK35" s="25"/>
+      <c r="BB35" s="180"/>
+      <c r="BC35" s="180"/>
+      <c r="BD35" s="180"/>
+      <c r="BE35" s="180"/>
+      <c r="BF35" s="180"/>
+      <c r="BG35" s="180"/>
+      <c r="BH35" s="180"/>
+      <c r="BI35" s="180"/>
+      <c r="BJ35" s="180"/>
+      <c r="BK35" s="21"/>
     </row>
     <row r="36" spans="1:63" ht="2.1" customHeight="1">
-      <c r="A36" s="11"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="59"/>
-      <c r="N36" s="59"/>
-      <c r="V36" s="45"/>
-      <c r="W36" s="45"/>
-      <c r="X36" s="45"/>
-      <c r="AO36" s="61"/>
-      <c r="AR36" s="56"/>
-      <c r="AS36" s="56"/>
-      <c r="AT36" s="56"/>
-      <c r="AU36" s="56"/>
-      <c r="AV36" s="56"/>
-      <c r="AW36" s="56"/>
-      <c r="AY36" s="59"/>
-      <c r="BK36" s="25"/>
+      <c r="A36" s="9"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="54"/>
+      <c r="N36" s="54"/>
+      <c r="V36" s="40"/>
+      <c r="W36" s="40"/>
+      <c r="X36" s="40"/>
+      <c r="AO36" s="56"/>
+      <c r="AR36" s="51"/>
+      <c r="AS36" s="51"/>
+      <c r="AT36" s="51"/>
+      <c r="AU36" s="51"/>
+      <c r="AV36" s="51"/>
+      <c r="AW36" s="51"/>
+      <c r="AY36" s="54"/>
+      <c r="BK36" s="21"/>
     </row>
     <row r="37" spans="1:63" ht="10.5" customHeight="1">
-      <c r="A37" s="11"/>
-      <c r="I37" s="233" t="s">
+      <c r="A37" s="9"/>
+      <c r="I37" s="234" t="s">
         <v>62</v>
       </c>
-      <c r="J37" s="234"/>
-      <c r="K37" s="234"/>
-      <c r="L37" s="234"/>
-      <c r="M37" s="234"/>
-      <c r="N37" s="234"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="235" t="s">
+      <c r="J37" s="235"/>
+      <c r="K37" s="235"/>
+      <c r="L37" s="235"/>
+      <c r="M37" s="235"/>
+      <c r="N37" s="235"/>
+      <c r="O37" s="64"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="236" t="s">
         <v>63</v>
       </c>
-      <c r="R37" s="235"/>
-      <c r="S37" s="235"/>
-      <c r="T37" s="235"/>
-      <c r="U37" s="235"/>
-      <c r="V37" s="235"/>
-      <c r="W37" s="235"/>
-      <c r="X37" s="235"/>
-      <c r="Y37" s="235"/>
-      <c r="Z37" s="47"/>
-      <c r="AA37" s="47"/>
-      <c r="AD37" s="236" t="s">
+      <c r="R37" s="236"/>
+      <c r="S37" s="236"/>
+      <c r="T37" s="236"/>
+      <c r="U37" s="236"/>
+      <c r="V37" s="236"/>
+      <c r="W37" s="236"/>
+      <c r="X37" s="236"/>
+      <c r="Y37" s="236"/>
+      <c r="Z37" s="42"/>
+      <c r="AA37" s="42"/>
+      <c r="AD37" s="237" t="s">
         <v>64</v>
       </c>
-      <c r="AE37" s="236"/>
-      <c r="AF37" s="236"/>
-      <c r="AG37" s="236"/>
-      <c r="AH37" s="236"/>
-      <c r="AI37" s="236"/>
-      <c r="AJ37" s="236"/>
-      <c r="AK37" s="236"/>
-      <c r="AL37" s="236"/>
-      <c r="AM37" s="236"/>
-      <c r="AO37" s="61"/>
-      <c r="AP37" s="67"/>
-      <c r="AR37" s="56" t="s">
+      <c r="AE37" s="237"/>
+      <c r="AF37" s="237"/>
+      <c r="AG37" s="237"/>
+      <c r="AH37" s="237"/>
+      <c r="AI37" s="237"/>
+      <c r="AJ37" s="237"/>
+      <c r="AK37" s="237"/>
+      <c r="AL37" s="237"/>
+      <c r="AM37" s="237"/>
+      <c r="AO37" s="56"/>
+      <c r="AP37" s="62"/>
+      <c r="AR37" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="AS37" s="56"/>
-      <c r="AT37" s="56"/>
-      <c r="AU37" s="56"/>
-      <c r="AV37" s="56"/>
-      <c r="AW37" s="56"/>
-      <c r="AY37" s="59"/>
-      <c r="BA37" s="176" t="s">
+      <c r="AS37" s="51"/>
+      <c r="AT37" s="51"/>
+      <c r="AU37" s="51"/>
+      <c r="AV37" s="51"/>
+      <c r="AW37" s="51"/>
+      <c r="AY37" s="54"/>
+      <c r="BA37" s="180" t="s">
         <v>46</v>
       </c>
-      <c r="BB37" s="176"/>
-      <c r="BC37" s="176"/>
-      <c r="BD37" s="176"/>
-      <c r="BE37" s="176"/>
-      <c r="BF37" s="176"/>
-      <c r="BG37" s="176"/>
-      <c r="BH37" s="176"/>
-      <c r="BI37" s="176"/>
-      <c r="BJ37" s="176"/>
-      <c r="BK37" s="25"/>
+      <c r="BB37" s="180"/>
+      <c r="BC37" s="180"/>
+      <c r="BD37" s="180"/>
+      <c r="BE37" s="180"/>
+      <c r="BF37" s="180"/>
+      <c r="BG37" s="180"/>
+      <c r="BH37" s="180"/>
+      <c r="BI37" s="180"/>
+      <c r="BJ37" s="180"/>
+      <c r="BK37" s="21"/>
     </row>
     <row r="38" spans="1:63" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A38" s="14"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="237" t="s">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="238" t="s">
         <v>47</v>
       </c>
-      <c r="J38" s="238"/>
-      <c r="K38" s="238"/>
-      <c r="L38" s="238"/>
-      <c r="M38" s="238"/>
-      <c r="N38" s="238"/>
-      <c r="O38" s="47"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="239" t="s">
+      <c r="J38" s="239"/>
+      <c r="K38" s="239"/>
+      <c r="L38" s="239"/>
+      <c r="M38" s="239"/>
+      <c r="N38" s="239"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="240" t="s">
         <v>48</v>
       </c>
-      <c r="R38" s="239"/>
-      <c r="S38" s="239"/>
-      <c r="T38" s="239"/>
-      <c r="U38" s="239"/>
-      <c r="V38" s="239"/>
-      <c r="W38" s="239"/>
-      <c r="X38" s="239"/>
-      <c r="Y38" s="239"/>
-      <c r="Z38" s="239"/>
-      <c r="AA38" s="239"/>
-      <c r="AB38" s="44"/>
-      <c r="AC38" s="44"/>
-      <c r="AD38" s="192" t="s">
+      <c r="R38" s="240"/>
+      <c r="S38" s="240"/>
+      <c r="T38" s="240"/>
+      <c r="U38" s="240"/>
+      <c r="V38" s="240"/>
+      <c r="W38" s="240"/>
+      <c r="X38" s="240"/>
+      <c r="Y38" s="240"/>
+      <c r="Z38" s="240"/>
+      <c r="AA38" s="240"/>
+      <c r="AB38" s="39"/>
+      <c r="AC38" s="39"/>
+      <c r="AD38" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="AE38" s="192"/>
-      <c r="AF38" s="192"/>
-      <c r="AG38" s="192"/>
-      <c r="AH38" s="192"/>
-      <c r="AI38" s="192"/>
-      <c r="AJ38" s="192"/>
-      <c r="AK38" s="192"/>
-      <c r="AL38" s="192"/>
-      <c r="AM38" s="192"/>
-      <c r="AN38" s="44"/>
-      <c r="AO38" s="70"/>
-      <c r="AP38" s="48"/>
-      <c r="AQ38" s="48"/>
-      <c r="AR38" s="48"/>
-      <c r="AS38" s="48"/>
-      <c r="AT38" s="48"/>
-      <c r="AU38" s="48"/>
-      <c r="AV38" s="48"/>
-      <c r="AW38" s="48"/>
-      <c r="AX38" s="48"/>
-      <c r="AY38" s="48"/>
-      <c r="AZ38" s="48"/>
-      <c r="BA38" s="48"/>
-      <c r="BB38" s="48"/>
-      <c r="BC38" s="48"/>
-      <c r="BD38" s="48"/>
-      <c r="BE38" s="48"/>
-      <c r="BF38" s="48"/>
-      <c r="BG38" s="48"/>
-      <c r="BH38" s="48"/>
-      <c r="BI38" s="48"/>
-      <c r="BJ38" s="48"/>
-      <c r="BK38" s="71"/>
+      <c r="AE38" s="196"/>
+      <c r="AF38" s="196"/>
+      <c r="AG38" s="196"/>
+      <c r="AH38" s="196"/>
+      <c r="AI38" s="196"/>
+      <c r="AJ38" s="196"/>
+      <c r="AK38" s="196"/>
+      <c r="AL38" s="196"/>
+      <c r="AM38" s="196"/>
+      <c r="AN38" s="39"/>
+      <c r="AO38" s="65"/>
+      <c r="AP38" s="43"/>
+      <c r="AQ38" s="43"/>
+      <c r="AR38" s="43"/>
+      <c r="AS38" s="43"/>
+      <c r="AT38" s="43"/>
+      <c r="AU38" s="43"/>
+      <c r="AV38" s="43"/>
+      <c r="AW38" s="43"/>
+      <c r="AX38" s="43"/>
+      <c r="AY38" s="43"/>
+      <c r="AZ38" s="43"/>
+      <c r="BA38" s="43"/>
+      <c r="BB38" s="43"/>
+      <c r="BC38" s="43"/>
+      <c r="BD38" s="43"/>
+      <c r="BE38" s="43"/>
+      <c r="BF38" s="43"/>
+      <c r="BG38" s="43"/>
+      <c r="BH38" s="43"/>
+      <c r="BI38" s="43"/>
+      <c r="BJ38" s="43"/>
+      <c r="BK38" s="66"/>
     </row>
     <row r="39" spans="1:63" ht="3.75" customHeight="1" thickBot="1">
-      <c r="A39" s="14"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="229"/>
-      <c r="J39" s="230"/>
-      <c r="K39" s="230"/>
-      <c r="L39" s="230"/>
-      <c r="M39" s="230"/>
-      <c r="N39" s="230"/>
-      <c r="O39" s="230"/>
-      <c r="P39" s="230"/>
-      <c r="Q39" s="230"/>
-      <c r="R39" s="72"/>
-      <c r="S39" s="72"/>
-      <c r="T39" s="72"/>
-      <c r="U39" s="72"/>
-      <c r="V39" s="73"/>
-      <c r="W39" s="73"/>
-      <c r="X39" s="73"/>
-      <c r="Y39" s="72"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="72"/>
-      <c r="AB39" s="72"/>
-      <c r="AC39" s="72"/>
-      <c r="AD39" s="72"/>
-      <c r="AE39" s="72"/>
-      <c r="AF39" s="72"/>
-      <c r="AG39" s="72"/>
-      <c r="AH39" s="72"/>
-      <c r="AI39" s="72"/>
-      <c r="AJ39" s="72"/>
-      <c r="AK39" s="72"/>
-      <c r="AL39" s="72"/>
-      <c r="AM39" s="72"/>
-      <c r="AN39" s="72"/>
-      <c r="AO39" s="72"/>
-      <c r="AP39" s="72"/>
-      <c r="AQ39" s="72"/>
-      <c r="AR39" s="72"/>
-      <c r="AS39" s="72"/>
-      <c r="AT39" s="72"/>
-      <c r="AU39" s="72"/>
-      <c r="AV39" s="72"/>
-      <c r="AW39" s="72"/>
-      <c r="AX39" s="72"/>
-      <c r="AY39" s="72"/>
-      <c r="AZ39" s="72"/>
-      <c r="BA39" s="72"/>
-      <c r="BB39" s="72"/>
-      <c r="BC39" s="72"/>
-      <c r="BD39" s="72"/>
-      <c r="BE39" s="72"/>
-      <c r="BF39" s="72"/>
-      <c r="BG39" s="72"/>
-      <c r="BH39" s="72"/>
-      <c r="BI39" s="72"/>
-      <c r="BJ39" s="72"/>
-      <c r="BK39" s="74"/>
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="231"/>
+      <c r="O39" s="231"/>
+      <c r="P39" s="231"/>
+      <c r="Q39" s="231"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="67"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="68"/>
+      <c r="W39" s="68"/>
+      <c r="X39" s="68"/>
+      <c r="Y39" s="67"/>
+      <c r="Z39" s="67"/>
+      <c r="AA39" s="67"/>
+      <c r="AB39" s="67"/>
+      <c r="AC39" s="67"/>
+      <c r="AD39" s="67"/>
+      <c r="AE39" s="67"/>
+      <c r="AF39" s="67"/>
+      <c r="AG39" s="67"/>
+      <c r="AH39" s="67"/>
+      <c r="AI39" s="67"/>
+      <c r="AJ39" s="67"/>
+      <c r="AK39" s="67"/>
+      <c r="AL39" s="67"/>
+      <c r="AM39" s="67"/>
+      <c r="AN39" s="67"/>
+      <c r="AO39" s="67"/>
+      <c r="AP39" s="67"/>
+      <c r="AQ39" s="67"/>
+      <c r="AR39" s="67"/>
+      <c r="AS39" s="67"/>
+      <c r="AT39" s="67"/>
+      <c r="AU39" s="67"/>
+      <c r="AV39" s="67"/>
+      <c r="AW39" s="67"/>
+      <c r="AX39" s="67"/>
+      <c r="AY39" s="67"/>
+      <c r="AZ39" s="67"/>
+      <c r="BA39" s="67"/>
+      <c r="BB39" s="67"/>
+      <c r="BC39" s="67"/>
+      <c r="BD39" s="67"/>
+      <c r="BE39" s="67"/>
+      <c r="BF39" s="67"/>
+      <c r="BG39" s="67"/>
+      <c r="BH39" s="67"/>
+      <c r="BI39" s="67"/>
+      <c r="BJ39" s="67"/>
+      <c r="BK39" s="69"/>
     </row>
     <row r="40" spans="1:63" ht="10.5" customHeight="1">
-      <c r="I40" s="231" t="s">
+      <c r="I40" s="232" t="s">
         <v>49</v>
       </c>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="232"/>
-      <c r="T40" s="232"/>
-      <c r="U40" s="232"/>
-      <c r="V40" s="232"/>
-      <c r="W40" s="232"/>
-      <c r="X40" s="232"/>
-      <c r="Y40" s="232"/>
-      <c r="Z40" s="232"/>
-      <c r="AA40" s="232"/>
-      <c r="AB40" s="232"/>
-      <c r="AC40" s="232"/>
-      <c r="AD40" s="232"/>
-      <c r="AE40" s="232"/>
-      <c r="AF40" s="232"/>
-      <c r="AG40" s="232"/>
-      <c r="AH40" s="232"/>
-      <c r="AI40" s="232"/>
-      <c r="AJ40" s="232"/>
-      <c r="AK40" s="232"/>
-      <c r="AL40" s="232"/>
-      <c r="AM40" s="232"/>
-      <c r="AN40" s="232"/>
-      <c r="AO40" s="232"/>
-      <c r="AP40" s="232"/>
-      <c r="AQ40" s="232"/>
-      <c r="AR40" s="232"/>
-      <c r="AS40" s="232"/>
-      <c r="AT40" s="232"/>
-      <c r="AU40" s="232"/>
-      <c r="AV40" s="232"/>
-      <c r="AW40" s="232"/>
-      <c r="AX40" s="232"/>
-      <c r="AY40" s="232"/>
-      <c r="AZ40" s="232"/>
-      <c r="BA40" s="232"/>
-      <c r="BB40" s="232"/>
-      <c r="BC40" s="232"/>
-      <c r="BD40" s="232"/>
-      <c r="BE40" s="232"/>
-      <c r="BF40" s="232"/>
-      <c r="BG40" s="232"/>
-      <c r="BH40" s="232"/>
-      <c r="BI40" s="232"/>
-      <c r="BJ40" s="232"/>
-      <c r="BK40" s="232"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="233"/>
+      <c r="N40" s="233"/>
+      <c r="O40" s="233"/>
+      <c r="P40" s="233"/>
+      <c r="Q40" s="233"/>
+      <c r="R40" s="233"/>
+      <c r="S40" s="233"/>
+      <c r="T40" s="233"/>
+      <c r="U40" s="233"/>
+      <c r="V40" s="233"/>
+      <c r="W40" s="233"/>
+      <c r="X40" s="233"/>
+      <c r="Y40" s="233"/>
+      <c r="Z40" s="233"/>
+      <c r="AA40" s="233"/>
+      <c r="AB40" s="233"/>
+      <c r="AC40" s="233"/>
+      <c r="AD40" s="233"/>
+      <c r="AE40" s="233"/>
+      <c r="AF40" s="233"/>
+      <c r="AG40" s="233"/>
+      <c r="AH40" s="233"/>
+      <c r="AI40" s="233"/>
+      <c r="AJ40" s="233"/>
+      <c r="AK40" s="233"/>
+      <c r="AL40" s="233"/>
+      <c r="AM40" s="233"/>
+      <c r="AN40" s="233"/>
+      <c r="AO40" s="233"/>
+      <c r="AP40" s="233"/>
+      <c r="AQ40" s="233"/>
+      <c r="AR40" s="233"/>
+      <c r="AS40" s="233"/>
+      <c r="AT40" s="233"/>
+      <c r="AU40" s="233"/>
+      <c r="AV40" s="233"/>
+      <c r="AW40" s="233"/>
+      <c r="AX40" s="233"/>
+      <c r="AY40" s="233"/>
+      <c r="AZ40" s="233"/>
+      <c r="BA40" s="233"/>
+      <c r="BB40" s="233"/>
+      <c r="BC40" s="233"/>
+      <c r="BD40" s="233"/>
+      <c r="BE40" s="233"/>
+      <c r="BF40" s="233"/>
+      <c r="BG40" s="233"/>
+      <c r="BH40" s="233"/>
+      <c r="BI40" s="233"/>
+      <c r="BJ40" s="233"/>
+      <c r="BK40" s="233"/>
     </row>
     <row r="41" spans="1:63" ht="13.95" customHeight="1">
-      <c r="K41" s="194"/>
-      <c r="L41" s="194"/>
-      <c r="M41" s="194"/>
-      <c r="N41" s="194"/>
-      <c r="O41" s="194"/>
-      <c r="P41" s="194"/>
-      <c r="Q41" s="194"/>
-      <c r="R41" s="194"/>
-      <c r="S41" s="194"/>
-      <c r="T41" s="194"/>
-      <c r="U41" s="194"/>
-      <c r="V41" s="194"/>
-      <c r="W41" s="194"/>
-      <c r="X41" s="194"/>
-      <c r="Y41" s="194"/>
-      <c r="Z41" s="194"/>
-      <c r="AA41" s="194"/>
-      <c r="AB41" s="194"/>
-      <c r="AC41" s="194"/>
-      <c r="AD41" s="194"/>
-      <c r="AE41" s="194"/>
-      <c r="AF41" s="194"/>
-      <c r="AG41" s="194"/>
-      <c r="AH41" s="194"/>
-      <c r="AI41" s="75"/>
-      <c r="AJ41" s="75"/>
-      <c r="AK41" s="75"/>
-      <c r="AL41" s="75"/>
-      <c r="AM41" s="194"/>
-      <c r="AN41" s="194"/>
-      <c r="AO41" s="194"/>
-      <c r="AP41" s="194"/>
-      <c r="AQ41" s="194"/>
-      <c r="AR41" s="194"/>
-      <c r="AS41" s="194"/>
-      <c r="AT41" s="194"/>
-      <c r="AU41" s="194"/>
-      <c r="AV41" s="194"/>
-      <c r="AW41" s="194"/>
-      <c r="AX41" s="194"/>
-      <c r="AY41" s="194"/>
-      <c r="AZ41" s="194"/>
-      <c r="BA41" s="194"/>
-      <c r="BB41" s="194"/>
-      <c r="BC41" s="194"/>
-      <c r="BD41" s="194"/>
-      <c r="BE41" s="194"/>
-      <c r="BF41" s="194"/>
-      <c r="BG41" s="194"/>
-      <c r="BH41" s="194"/>
-      <c r="BI41" s="194"/>
-      <c r="BJ41" s="194"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="198"/>
+      <c r="O41" s="198"/>
+      <c r="P41" s="198"/>
+      <c r="Q41" s="198"/>
+      <c r="R41" s="198"/>
+      <c r="S41" s="198"/>
+      <c r="T41" s="198"/>
+      <c r="U41" s="198"/>
+      <c r="V41" s="198"/>
+      <c r="W41" s="198"/>
+      <c r="X41" s="198"/>
+      <c r="Y41" s="198"/>
+      <c r="Z41" s="198"/>
+      <c r="AA41" s="198"/>
+      <c r="AB41" s="198"/>
+      <c r="AC41" s="198"/>
+      <c r="AD41" s="198"/>
+      <c r="AE41" s="198"/>
+      <c r="AF41" s="198"/>
+      <c r="AG41" s="198"/>
+      <c r="AH41" s="198"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="70"/>
+      <c r="AK41" s="70"/>
+      <c r="AL41" s="70"/>
+      <c r="AM41" s="198"/>
+      <c r="AN41" s="198"/>
+      <c r="AO41" s="198"/>
+      <c r="AP41" s="198"/>
+      <c r="AQ41" s="198"/>
+      <c r="AR41" s="198"/>
+      <c r="AS41" s="198"/>
+      <c r="AT41" s="198"/>
+      <c r="AU41" s="198"/>
+      <c r="AV41" s="198"/>
+      <c r="AW41" s="198"/>
+      <c r="AX41" s="198"/>
+      <c r="AY41" s="198"/>
+      <c r="AZ41" s="198"/>
+      <c r="BA41" s="198"/>
+      <c r="BB41" s="198"/>
+      <c r="BC41" s="198"/>
+      <c r="BD41" s="198"/>
+      <c r="BE41" s="198"/>
+      <c r="BF41" s="198"/>
+      <c r="BG41" s="198"/>
+      <c r="BH41" s="198"/>
+      <c r="BI41" s="198"/>
+      <c r="BJ41" s="198"/>
     </row>
     <row r="42" spans="1:63" ht="13.95" customHeight="1">
-      <c r="K42" s="194"/>
-      <c r="L42" s="194"/>
-      <c r="M42" s="194"/>
-      <c r="N42" s="194"/>
-      <c r="O42" s="194"/>
-      <c r="P42" s="194"/>
-      <c r="Q42" s="194"/>
-      <c r="R42" s="194"/>
-      <c r="S42" s="194"/>
-      <c r="T42" s="194"/>
-      <c r="U42" s="194"/>
-      <c r="V42" s="194"/>
-      <c r="W42" s="194"/>
-      <c r="X42" s="194"/>
-      <c r="Y42" s="194"/>
-      <c r="Z42" s="194"/>
-      <c r="AA42" s="194"/>
-      <c r="AB42" s="194"/>
-      <c r="AC42" s="194"/>
-      <c r="AD42" s="194"/>
-      <c r="AE42" s="194"/>
-      <c r="AF42" s="194"/>
-      <c r="AG42" s="194"/>
-      <c r="AH42" s="194"/>
-      <c r="AI42" s="75"/>
-      <c r="AJ42" s="75"/>
-      <c r="AK42" s="75"/>
-      <c r="AL42" s="75"/>
-      <c r="AM42" s="194"/>
-      <c r="AN42" s="194"/>
-      <c r="AO42" s="194"/>
-      <c r="AP42" s="194"/>
-      <c r="AQ42" s="194"/>
-      <c r="AR42" s="194"/>
-      <c r="AS42" s="194"/>
-      <c r="AT42" s="194"/>
-      <c r="AU42" s="194"/>
-      <c r="AV42" s="194"/>
-      <c r="AW42" s="194"/>
-      <c r="AX42" s="194"/>
-      <c r="AY42" s="194"/>
-      <c r="AZ42" s="194"/>
-      <c r="BA42" s="194"/>
-      <c r="BB42" s="194"/>
-      <c r="BC42" s="194"/>
-      <c r="BD42" s="194"/>
-      <c r="BE42" s="194"/>
-      <c r="BF42" s="194"/>
-      <c r="BG42" s="194"/>
-      <c r="BH42" s="194"/>
-      <c r="BI42" s="194"/>
-      <c r="BJ42" s="194"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="198"/>
+      <c r="O42" s="198"/>
+      <c r="P42" s="198"/>
+      <c r="Q42" s="198"/>
+      <c r="R42" s="198"/>
+      <c r="S42" s="198"/>
+      <c r="T42" s="198"/>
+      <c r="U42" s="198"/>
+      <c r="V42" s="198"/>
+      <c r="W42" s="198"/>
+      <c r="X42" s="198"/>
+      <c r="Y42" s="198"/>
+      <c r="Z42" s="198"/>
+      <c r="AA42" s="198"/>
+      <c r="AB42" s="198"/>
+      <c r="AC42" s="198"/>
+      <c r="AD42" s="198"/>
+      <c r="AE42" s="198"/>
+      <c r="AF42" s="198"/>
+      <c r="AG42" s="198"/>
+      <c r="AH42" s="198"/>
+      <c r="AI42" s="70"/>
+      <c r="AJ42" s="70"/>
+      <c r="AK42" s="70"/>
+      <c r="AL42" s="70"/>
+      <c r="AM42" s="198"/>
+      <c r="AN42" s="198"/>
+      <c r="AO42" s="198"/>
+      <c r="AP42" s="198"/>
+      <c r="AQ42" s="198"/>
+      <c r="AR42" s="198"/>
+      <c r="AS42" s="198"/>
+      <c r="AT42" s="198"/>
+      <c r="AU42" s="198"/>
+      <c r="AV42" s="198"/>
+      <c r="AW42" s="198"/>
+      <c r="AX42" s="198"/>
+      <c r="AY42" s="198"/>
+      <c r="AZ42" s="198"/>
+      <c r="BA42" s="198"/>
+      <c r="BB42" s="198"/>
+      <c r="BC42" s="198"/>
+      <c r="BD42" s="198"/>
+      <c r="BE42" s="198"/>
+      <c r="BF42" s="198"/>
+      <c r="BG42" s="198"/>
+      <c r="BH42" s="198"/>
+      <c r="BI42" s="198"/>
+      <c r="BJ42" s="198"/>
     </row>
     <row r="44" spans="1:63" ht="13.95" customHeight="1">
-      <c r="I44" s="76"/>
+      <c r="I44" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="184">
@@ -6582,7 +6612,6 @@
     <mergeCell ref="K41:AH42"/>
     <mergeCell ref="AM41:BJ42"/>
     <mergeCell ref="AO26:BK27"/>
-    <mergeCell ref="N1:AR4"/>
     <mergeCell ref="I5:M6"/>
     <mergeCell ref="O5:AR6"/>
     <mergeCell ref="M11:AC12"/>
@@ -6735,6 +6764,12 @@
     <mergeCell ref="AL14:AO14"/>
     <mergeCell ref="AD13:AG13"/>
     <mergeCell ref="AD14:AG14"/>
+    <mergeCell ref="AD12:AG12"/>
+    <mergeCell ref="AH12:AK12"/>
+    <mergeCell ref="AL12:AO12"/>
+    <mergeCell ref="AP12:AS12"/>
+    <mergeCell ref="AT12:AW12"/>
+    <mergeCell ref="AX12:BA12"/>
     <mergeCell ref="AS1:AZ1"/>
     <mergeCell ref="BB1:BK1"/>
     <mergeCell ref="AS2:AZ2"/>
@@ -6745,6 +6780,7 @@
     <mergeCell ref="BB4:BK4"/>
     <mergeCell ref="AS5:AZ5"/>
     <mergeCell ref="BB5:BK5"/>
+    <mergeCell ref="I1:AR4"/>
     <mergeCell ref="AS6:AZ6"/>
     <mergeCell ref="BB6:BK6"/>
     <mergeCell ref="T8:AE8"/>
@@ -6753,12 +6789,6 @@
     <mergeCell ref="AW9:BH9"/>
     <mergeCell ref="AD11:AO11"/>
     <mergeCell ref="AP11:BA11"/>
-    <mergeCell ref="AD12:AG12"/>
-    <mergeCell ref="AH12:AK12"/>
-    <mergeCell ref="AL12:AO12"/>
-    <mergeCell ref="AP12:AS12"/>
-    <mergeCell ref="AT12:AW12"/>
-    <mergeCell ref="AX12:BA12"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD35:AL35 AD37" xr:uid="{00000000-0002-0000-0000-000000000000}">
